--- a/01_Thermal/B_results/single_var_params_pchip.xlsx
+++ b/01_Thermal/B_results/single_var_params_pchip.xlsx
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>0.01</v>
       </c>
       <c r="B3" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>0.02</v>
       </c>
       <c r="B4" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>0.03</v>
       </c>
       <c r="B5" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>0.04</v>
       </c>
       <c r="B6" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>0.05</v>
       </c>
       <c r="B7" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>0.06</v>
       </c>
       <c r="B8" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>0.08</v>
       </c>
       <c r="B10" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>0.09</v>
       </c>
       <c r="B11" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>0.11</v>
       </c>
       <c r="B13" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>0.12</v>
       </c>
       <c r="B14" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>0.13</v>
       </c>
       <c r="B15" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>0.14</v>
       </c>
       <c r="B16" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>0.15</v>
       </c>
       <c r="B17" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>0.16</v>
       </c>
       <c r="B18" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>0.17</v>
       </c>
       <c r="B19" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>0.18</v>
       </c>
       <c r="B20" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>0.19</v>
       </c>
       <c r="B21" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>0.2</v>
       </c>
       <c r="B22" t="n">
-        <v>9.818716009997178</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>0.21</v>
       </c>
       <c r="B23" t="n">
-        <v>9.526200922525211</v>
+        <v>9.266906142249669</v>
       </c>
       <c r="C23" t="n">
-        <v>0.369024576921719</v>
+        <v>0.3837327751305098</v>
       </c>
       <c r="D23" t="n">
-        <v>0.09764366287132586</v>
+        <v>0.03178820574602507</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>0.22</v>
       </c>
       <c r="B24" t="n">
-        <v>9.247769081303483</v>
+        <v>9.141753560320318</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3774491508103028</v>
+        <v>0.3900712197477076</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08725176679060787</v>
+        <v>0.02864484553237209</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>0.23</v>
       </c>
       <c r="B25" t="n">
-        <v>8.98310452647716</v>
+        <v>9.000511439155895</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3859360131097643</v>
+        <v>0.3966522974439409</v>
       </c>
       <c r="D25" t="n">
-        <v>0.07705229046522198</v>
+        <v>0.02556957801983926</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>0.24</v>
       </c>
       <c r="B26" t="n">
-        <v>8.731888906542457</v>
+        <v>8.844992041707304</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3944760777455458</v>
+        <v>0.4034816360997915</v>
       </c>
       <c r="D26" t="n">
-        <v>0.06713552104693438</v>
+        <v>0.02258369547895867</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>0.25</v>
       </c>
       <c r="B27" t="n">
-        <v>8.49380444464628</v>
+        <v>8.677006656978232</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4030596918714887</v>
+        <v>0.4105650600138718</v>
       </c>
       <c r="D27" t="n">
-        <v>0.05759174568751119</v>
+        <v>0.01970849018026235</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>0.26</v>
       </c>
       <c r="B28" t="n">
-        <v>8.268536678445914</v>
+        <v>8.498343612341074</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4116766336867099</v>
+        <v>0.4179085895709392</v>
       </c>
       <c r="D28" t="n">
-        <v>0.04851125153871861</v>
+        <v>0.01696525439428237</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>0.27</v>
       </c>
       <c r="B29" t="n">
-        <v>8.055776992450204</v>
+        <v>8.310748911901523</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4203161124393482</v>
+        <v>0.425518440776633</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03998432575232277</v>
+        <v>0.01437528039155081</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>0.28</v>
       </c>
       <c r="B30" t="n">
-        <v>7.855224962734662</v>
+        <v>8.11590959063814</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4289667707674991</v>
+        <v>0.4334010246329185</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03210125548008987</v>
+        <v>0.01195986044259971</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>0.29</v>
       </c>
       <c r="B31" t="n">
-        <v>7.666590534731651</v>
+        <v>7.915439798980379</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4376166895244373</v>
+        <v>0.4415629463275865</v>
       </c>
       <c r="D31" t="n">
-        <v>0.02495232787378608</v>
+        <v>0.009740286817961149</v>
       </c>
     </row>
     <row r="32">
@@ -875,13 +875,13 @@
         <v>0.3</v>
       </c>
       <c r="B32" t="n">
-        <v>7.489596055487631</v>
+        <v>7.710869567344367</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4462533952306689</v>
+        <v>0.4500110042103748</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01862783008517749</v>
+        <v>0.007737851788167168</v>
       </c>
     </row>
     <row r="33">
@@ -889,13 +889,13 @@
         <v>0.31</v>
       </c>
       <c r="B33" t="n">
-        <v>7.323978182394116</v>
+        <v>7.503636145521822</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4548638702893971</v>
+        <v>0.4587521885274574</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0132180492660303</v>
+        <v>0.005973847623749844</v>
       </c>
     </row>
     <row r="34">
@@ -903,13 +903,13 @@
         <v>0.32</v>
       </c>
       <c r="B34" t="n">
-        <v>7.169489690980239</v>
+        <v>7.295077767847513</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4634345660945506</v>
+        <v>0.467793679885191</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00881327256811067</v>
+        <v>0.004469566595241236</v>
       </c>
     </row>
     <row r="35">
@@ -917,13 +917,13 @@
         <v>0.33</v>
       </c>
       <c r="B35" t="n">
-        <v>7.02590120494453</v>
+        <v>7.086429661493749</v>
       </c>
       <c r="C35" t="n">
-        <v>0.471951419151553</v>
+        <v>0.477142847413119</v>
       </c>
       <c r="D35" t="n">
-        <v>0.005503787143184762</v>
+        <v>0.00324630097317341</v>
       </c>
     </row>
     <row r="36">
@@ -931,13 +931,13 @@
         <v>0.34</v>
       </c>
       <c r="B36" t="n">
-        <v>6.893002872244152</v>
+        <v>6.878822091479354</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4803998703204526</v>
+        <v>0.4868072465953205</v>
       </c>
       <c r="D36" t="n">
-        <v>0.003379880143018744</v>
+        <v>0.002325343028078415</v>
       </c>
     </row>
     <row r="37">
@@ -945,13 +945,13 @@
         <v>0.35</v>
       </c>
       <c r="B37" t="n">
-        <v>6.770606011794624</v>
+        <v>6.673280221219097</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4887648872788611</v>
+        <v>0.496794616738258</v>
       </c>
       <c r="D37" t="n">
-        <v>0.002531838719378787</v>
+        <v>0.001727985030488321</v>
       </c>
     </row>
     <row r="38">
@@ -959,13 +959,13 @@
         <v>0.36</v>
       </c>
       <c r="B38" t="n">
-        <v>6.6578640993808</v>
+        <v>6.439511126847631</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4973759271480145</v>
+        <v>0.5079599122513961</v>
       </c>
       <c r="D38" t="n">
-        <v>0.002357603478376026</v>
+        <v>0.001309426355554675</v>
       </c>
     </row>
     <row r="39">
@@ -973,13 +973,13 @@
         <v>0.37</v>
       </c>
       <c r="B39" t="n">
-        <v>6.553324738204014</v>
+        <v>6.158322469410741</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5065029742516405</v>
+        <v>0.5210010356552146</v>
       </c>
       <c r="D39" t="n">
-        <v>0.002194965034119759</v>
+        <v>0.0009114864327318508</v>
       </c>
     </row>
     <row r="40">
@@ -987,13 +987,13 @@
         <v>0.38</v>
       </c>
       <c r="B40" t="n">
-        <v>6.455962935499727</v>
+        <v>5.846619879040374</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5160355334815303</v>
+        <v>0.535678970697947</v>
       </c>
       <c r="D40" t="n">
-        <v>0.00204398555037331</v>
+        <v>0.0005353876140061542</v>
       </c>
     </row>
     <row r="41">
@@ -1001,13 +1001,13 @@
         <v>0.39</v>
       </c>
       <c r="B41" t="n">
-        <v>6.364820207629515</v>
+        <v>5.519720768018117</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5258543595100447</v>
+        <v>0.5517314584882074</v>
       </c>
       <c r="D41" t="n">
-        <v>0.001904727190900005</v>
+        <v>0.0001823522513638887</v>
       </c>
     </row>
     <row r="42">
@@ -1015,13 +1015,13 @@
         <v>0.4</v>
       </c>
       <c r="B42" t="n">
-        <v>6.27899621783582</v>
+        <v>5.19082139831256</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5358305950952313</v>
+        <v>0.5688638164696814</v>
       </c>
       <c r="D42" t="n">
-        <v>0.001777252119463168</v>
+        <v>-0.0001463973032086422</v>
       </c>
     </row>
     <row r="43">
@@ -1029,13 +1029,13 @@
         <v>0.41</v>
       </c>
       <c r="B43" t="n">
-        <v>6.197641748866521</v>
+        <v>4.870782145401046</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5458252069380491</v>
+        <v>0.5867411704754066</v>
       </c>
       <c r="D43" t="n">
-        <v>0.001661622499826124</v>
+        <v>-0.0004496386977251343</v>
       </c>
     </row>
     <row r="44">
@@ -1043,13 +1043,13 @@
         <v>0.42</v>
       </c>
       <c r="B44" t="n">
-        <v>6.119952874200386</v>
+        <v>4.568166006556644</v>
       </c>
       <c r="C44" t="n">
-        <v>0.555688762859303</v>
+        <v>0.6049824535957234</v>
       </c>
       <c r="D44" t="n">
-        <v>0.001557900495752198</v>
+        <v>-0.0007261495801992837</v>
       </c>
     </row>
     <row r="45">
@@ -1057,13 +1057,13 @@
         <v>0.43</v>
       </c>
       <c r="B45" t="n">
-        <v>6.045166213361524</v>
+        <v>4.289458944864753</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5652615968629845</v>
+        <v>0.6231566497359644</v>
       </c>
       <c r="D45" t="n">
-        <v>0.001466148271004713</v>
+        <v>-0.0009747075986447885</v>
       </c>
     </row>
     <row r="46">
@@ -1071,13 +1071,13 @@
         <v>0.44</v>
       </c>
       <c r="B46" t="n">
-        <v>5.972555174302229</v>
+        <v>4.039406228876048</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5743744087744883</v>
+        <v>0.6407818506434462</v>
       </c>
       <c r="D46" t="n">
-        <v>0.001386427989346995</v>
+        <v>-0.001194090401075345</v>
       </c>
     </row>
     <row r="47">
@@ -1085,13 +1085,13 @@
         <v>0.45</v>
       </c>
       <c r="B47" t="n">
-        <v>5.901427099610316</v>
+        <v>3.821411762069222</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5828493421046894</v>
+        <v>0.6573277391240538</v>
       </c>
       <c r="D47" t="n">
-        <v>0.001318801814542369</v>
+        <v>-0.001383075635504648</v>
       </c>
     </row>
     <row r="48">
@@ -1099,13 +1099,13 @@
         <v>0.46</v>
       </c>
       <c r="B48" t="n">
-        <v>5.831121243809804</v>
+        <v>3.637963548118323</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5905015771354417</v>
+        <v>0.6722220919519383</v>
       </c>
       <c r="D48" t="n">
-        <v>0.001263331910354159</v>
+        <v>-0.001540440949946395</v>
       </c>
     </row>
     <row r="49">
@@ -1113,13 +1113,13 @@
         <v>0.47</v>
       </c>
       <c r="B49" t="n">
-        <v>5.761007516646194</v>
+        <v>3.491065237641059</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5971414655649976</v>
+        <v>0.6848617970491815</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00122008044054569</v>
+        <v>-0.001664963992414283</v>
       </c>
     </row>
     <row r="50">
@@ -1127,13 +1127,13 @@
         <v>0.48</v>
       </c>
       <c r="B50" t="n">
-        <v>5.690485932297332</v>
+        <v>3.382669848614425</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6025772181433997</v>
+        <v>0.6946286868792535</v>
       </c>
       <c r="D50" t="n">
-        <v>0.001189109568880286</v>
+        <v>-0.001755422410922006</v>
       </c>
     </row>
     <row r="51">
@@ -1141,13 +1141,13 @@
         <v>0.49</v>
       </c>
       <c r="B51" t="n">
-        <v>5.618986707206526</v>
+        <v>3.315127215245221</v>
       </c>
       <c r="C51" t="n">
-        <v>0.6066181375159856</v>
+        <v>0.7009101958506121</v>
       </c>
       <c r="D51" t="n">
-        <v>0.001170481459121273</v>
+        <v>-0.001810593853483264</v>
       </c>
     </row>
     <row r="52">
@@ -1155,13 +1155,13 @@
         <v>0.5</v>
       </c>
       <c r="B52" t="n">
-        <v>5.545970949951866</v>
+        <v>3.291672626834771</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6090783651875445</v>
+        <v>0.7031244562920843</v>
       </c>
       <c r="D52" t="n">
-        <v>0.001164258275031974</v>
+        <v>-0.00182925596811175</v>
       </c>
     </row>
     <row r="53">
@@ -1169,13 +1169,13 @@
         <v>0.51</v>
       </c>
       <c r="B53" t="n">
-        <v>5.471887569997465</v>
+        <v>3.294340133802699</v>
       </c>
       <c r="C53" t="n">
-        <v>0.6106170180443559</v>
+        <v>0.7028327576507084</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00121220304002133</v>
+        <v>-0.001777971988568453</v>
       </c>
     </row>
     <row r="54">
@@ -1183,13 +1183,13 @@
         <v>0.52</v>
       </c>
       <c r="B54" t="n">
-        <v>5.397655829558688</v>
+        <v>3.302062485392739</v>
       </c>
       <c r="C54" t="n">
-        <v>0.6120192882089399</v>
+        <v>0.7019903089190265</v>
       </c>
       <c r="D54" t="n">
-        <v>0.001350783114168646</v>
+        <v>-0.001629740212080293</v>
       </c>
     </row>
     <row r="55">
@@ -1197,13 +1197,13 @@
         <v>0.53</v>
       </c>
       <c r="B55" t="n">
-        <v>5.323459643190905</v>
+        <v>3.314433850651592</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6132946816612818</v>
+        <v>0.7006468803934559</v>
       </c>
       <c r="D55" t="n">
-        <v>0.001572117166242795</v>
+        <v>-0.001392990881859867</v>
       </c>
     </row>
     <row r="56">
@@ -1211,13 +1211,13 @@
         <v>0.54</v>
       </c>
       <c r="B56" t="n">
-        <v>5.249474135756598</v>
+        <v>3.331062739610732</v>
       </c>
       <c r="C56" t="n">
-        <v>0.6144528747652864</v>
+        <v>0.6988530200712686</v>
       </c>
       <c r="D56" t="n">
-        <v>0.001868323865012651</v>
+        <v>-0.001076154241119771</v>
       </c>
     </row>
     <row r="57">
@@ -1225,13 +1225,13 @@
         <v>0.55</v>
       </c>
       <c r="B57" t="n">
-        <v>5.17586566655557</v>
+        <v>3.351566394653734</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6155036942392977</v>
+        <v>0.696659720127897</v>
       </c>
       <c r="D57" t="n">
-        <v>0.002231521879247086</v>
+        <v>-0.0006876605330726024</v>
       </c>
     </row>
     <row r="58">
@@ -1239,13 +1239,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58" t="n">
-        <v>5.102791907861339</v>
+        <v>3.37556573177956</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6164570986041712</v>
+        <v>0.6941181172190631</v>
       </c>
       <c r="D58" t="n">
-        <v>0.002653829877714974</v>
+        <v>-0.0002359400009309583</v>
       </c>
     </row>
     <row r="59">
@@ -1253,13 +1253,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59" t="n">
-        <v>5.030401973365652</v>
+        <v>3.402680785301913</v>
       </c>
       <c r="C59" t="n">
-        <v>0.617323161168692</v>
+        <v>0.6912792279321825</v>
       </c>
       <c r="D59" t="n">
-        <v>0.003127366529185186</v>
+        <v>0.0002705771120925647</v>
       </c>
     </row>
     <row r="60">
@@ -1267,13 +1267,13 @@
         <v>0.58</v>
       </c>
       <c r="B60" t="n">
-        <v>4.958836592112735</v>
+        <v>3.432526626794585</v>
       </c>
       <c r="C60" t="n">
-        <v>0.6181120546039535</v>
+        <v>0.6881937201624881</v>
       </c>
       <c r="D60" t="n">
-        <v>0.003644250502426591</v>
+        <v>0.000823460562785364</v>
       </c>
     </row>
     <row r="61">
@@ -1281,13 +1281,13 @@
         <v>0.59</v>
       </c>
       <c r="B61" t="n">
-        <v>4.888228323624999</v>
+        <v>3.464709744374095</v>
       </c>
       <c r="C61" t="n">
-        <v>0.618834037150789</v>
+        <v>0.684911720706145</v>
       </c>
       <c r="D61" t="n">
-        <v>0.004196600466208073</v>
+        <v>0.001414280107934854</v>
       </c>
     </row>
     <row r="62">
@@ -1295,13 +1295,13 @@
         <v>0.6</v>
       </c>
       <c r="B62" t="n">
-        <v>4.81870181007735</v>
+        <v>3.498824881934597</v>
       </c>
       <c r="C62" t="n">
-        <v>0.6194994404975396</v>
+        <v>0.6814826589486265</v>
       </c>
       <c r="D62" t="n">
-        <v>0.004776535089298499</v>
+        <v>0.002034605504328434</v>
       </c>
     </row>
     <row r="63">
@@ -1309,13 +1309,13 @@
         <v>0.61</v>
       </c>
       <c r="B63" t="n">
-        <v>4.75037406156308</v>
+        <v>3.534452349844595</v>
       </c>
       <c r="C63" t="n">
-        <v>0.6201186593593633</v>
+        <v>0.6779551461834216</v>
       </c>
       <c r="D63" t="n">
-        <v>0.005376173040466744</v>
+        <v>0.002676006508753506</v>
       </c>
     </row>
     <row r="64">
@@ -1323,13 +1323,13 @@
         <v>0.62</v>
       </c>
       <c r="B64" t="n">
-        <v>4.683354770706006</v>
+        <v>3.571155828920644</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6207021427849855</v>
+        <v>0.6743768898239199</v>
       </c>
       <c r="D64" t="n">
-        <v>0.005987632988481677</v>
+        <v>0.003330052877997472</v>
       </c>
     </row>
     <row r="65">
@@ -1337,13 +1337,13 @@
         <v>0.63</v>
       </c>
       <c r="B65" t="n">
-        <v>4.617746653106796</v>
+        <v>3.608480698172706</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6212603872122726</v>
+        <v>0.6707946415690466</v>
       </c>
       <c r="D65" t="n">
-        <v>0.006603033602112177</v>
+        <v>0.003988314368847737</v>
       </c>
     </row>
     <row r="66">
@@ -1351,13 +1351,13 @@
         <v>0.64</v>
       </c>
       <c r="B66" t="n">
-        <v>4.553645810362252</v>
+        <v>3.645952923765881</v>
       </c>
       <c r="C66" t="n">
-        <v>0.621803931290309</v>
+        <v>0.667254178448991</v>
       </c>
       <c r="D66" t="n">
-        <v>0.00721449355012711</v>
+        <v>0.004642360738091702</v>
       </c>
     </row>
     <row r="67">
@@ -1365,13 +1365,13 @@
         <v>0.65</v>
       </c>
       <c r="B67" t="n">
-        <v>4.491142112661271</v>
+        <v>3.683078551705571</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6223433524827744</v>
+        <v>0.6638003156085978</v>
       </c>
       <c r="D67" t="n">
-        <v>0.007814131501295354</v>
+        <v>0.005283761742516773</v>
       </c>
     </row>
     <row r="68">
@@ -1379,13 +1379,13 @@
         <v>0.66</v>
       </c>
       <c r="B68" t="n">
-        <v>4.43031959823692</v>
+        <v>3.719343849727029</v>
       </c>
       <c r="C68" t="n">
-        <v>0.622889265465386</v>
+        <v>0.6604769496797225</v>
       </c>
       <c r="D68" t="n">
-        <v>0.008394066124385782</v>
+        <v>0.005904087138910353</v>
       </c>
     </row>
     <row r="69">
@@ -1393,13 +1393,13 @@
         <v>0.67</v>
       </c>
       <c r="B69" t="n">
-        <v>4.371256887237883</v>
+        <v>3.754216144525852</v>
       </c>
       <c r="C69" t="n">
-        <v>0.6234523223289712</v>
+        <v>0.6573271316469973</v>
       </c>
       <c r="D69" t="n">
-        <v>0.008946416088167264</v>
+        <v>0.006494906684059843</v>
       </c>
     </row>
     <row r="70">
@@ -1407,13 +1407,13 @@
         <v>0.68</v>
       </c>
       <c r="B70" t="n">
-        <v>4.314027607871984</v>
+        <v>3.787145398560712</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6240432145994083</v>
+        <v>0.6543931682209666</v>
       </c>
       <c r="D70" t="n">
-        <v>0.009463300061408674</v>
+        <v>0.00704779013475265</v>
       </c>
     </row>
     <row r="71">
@@ -1421,13 +1421,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71" t="n">
-        <v>4.258700832967609</v>
+        <v>3.817566565955599</v>
       </c>
       <c r="C71" t="n">
-        <v>0.6246726770862049</v>
+        <v>0.6517167508957521</v>
       </c>
       <c r="D71" t="n">
-        <v>0.009936836712878885</v>
+        <v>0.007554307247776173</v>
       </c>
     </row>
     <row r="72">
@@ -1435,13 +1435,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72" t="n">
-        <v>4.205341525394056</v>
+        <v>3.844902759313665</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6253514935728869</v>
+        <v>0.6493391120830642</v>
       </c>
       <c r="D72" t="n">
-        <v>0.01035914471134677</v>
+        <v>0.008006027779917815</v>
       </c>
     </row>
     <row r="73">
@@ -1449,13 +1449,13 @@
         <v>0.71</v>
       </c>
       <c r="B73" t="n">
-        <v>4.15401099107789</v>
+        <v>3.868569248363364</v>
       </c>
       <c r="C73" t="n">
-        <v>0.6260905043646579</v>
+        <v>0.6473012079789716</v>
       </c>
       <c r="D73" t="n">
-        <v>0.01072234272558121</v>
+        <v>0.008394521487964983</v>
       </c>
     </row>
     <row r="74">
@@ -1463,13 +1463,13 @@
         <v>0.72</v>
       </c>
       <c r="B74" t="n">
-        <v>4.104767338648576</v>
+        <v>3.887978297196585</v>
       </c>
       <c r="C74" t="n">
-        <v>0.626900615711975</v>
+        <v>0.6456439281337443</v>
       </c>
       <c r="D74" t="n">
-        <v>0.01101854942435106</v>
+        <v>0.008711358128705078</v>
       </c>
     </row>
     <row r="75">
@@ -1477,13 +1477,13 @@
         <v>0.73</v>
       </c>
       <c r="B75" t="n">
-        <v>4.057665945042448</v>
+        <v>3.902544829430874</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6277928111327666</v>
+        <v>0.6444083320587046</v>
       </c>
       <c r="D75" t="n">
-        <v>0.01123988347642521</v>
+        <v>0.008948107458925502</v>
       </c>
     </row>
     <row r="76">
@@ -1491,13 +1491,13 @@
         <v>0.74</v>
       </c>
       <c r="B76" t="n">
-        <v>4.012759926689583</v>
+        <v>3.911692890057502</v>
       </c>
       <c r="C76" t="n">
-        <v>0.6287781646610329</v>
+        <v>0.6436359136190138</v>
       </c>
       <c r="D76" t="n">
-        <v>0.01137846355057252</v>
+        <v>0.009096339235413663</v>
       </c>
     </row>
     <row r="77">
@@ -1505,13 +1505,13 @@
         <v>0.75</v>
       </c>
       <c r="B77" t="n">
-        <v>3.970100616203556</v>
+        <v>3.914862849292072</v>
       </c>
       <c r="C77" t="n">
-        <v>0.6298678560555186</v>
+        <v>0.6433688944307844</v>
       </c>
       <c r="D77" t="n">
-        <v>0.01142640831556188</v>
+        <v>0.009147623214956957</v>
       </c>
     </row>
     <row r="78">
@@ -1519,13 +1519,13 @@
         <v>0.76</v>
       </c>
       <c r="B78" t="n">
-        <v>3.928333919957582</v>
+        <v>3.912453049582274</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6311097653179407</v>
+        <v>0.6434766041867984</v>
       </c>
       <c r="D78" t="n">
-        <v>0.01140891185614707</v>
+        <v>0.009130260273394541</v>
       </c>
     </row>
     <row r="79">
@@ -1533,13 +1533,13 @@
         <v>0.77</v>
       </c>
       <c r="B79" t="n">
-        <v>3.886169578025862</v>
+        <v>3.905419317376539</v>
       </c>
       <c r="C79" t="n">
-        <v>0.6325363509695623</v>
+        <v>0.6437926201761982</v>
       </c>
       <c r="D79" t="n">
-        <v>0.01135738442668268</v>
+        <v>0.009079248834159247</v>
       </c>
     </row>
     <row r="80">
@@ -1547,13 +1547,13 @@
         <v>0.78</v>
       </c>
       <c r="B80" t="n">
-        <v>3.843749696290867</v>
+        <v>3.894065929626136</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6341357836955965</v>
+        <v>0.6443064083977385</v>
       </c>
       <c r="D80" t="n">
-        <v>0.01127326895033876</v>
+        <v>0.008996204975429006</v>
       </c>
     </row>
     <row r="81">
@@ -1561,13 +1561,13 @@
         <v>0.79</v>
       </c>
       <c r="B81" t="n">
-        <v>3.801211055381283</v>
+        <v>3.878708877619875</v>
       </c>
       <c r="C81" t="n">
-        <v>0.6358962513332361</v>
+        <v>0.6450075893803975</v>
       </c>
       <c r="D81" t="n">
-        <v>0.01115800835028537</v>
+        <v>0.008882744775381753</v>
       </c>
     </row>
     <row r="82">
@@ -1575,13 +1575,13 @@
         <v>0.8</v>
       </c>
       <c r="B82" t="n">
-        <v>3.758685041993198</v>
+        <v>3.8596726900856</v>
       </c>
       <c r="C82" t="n">
-        <v>0.6378059260692855</v>
+        <v>0.6458859064539157</v>
       </c>
       <c r="D82" t="n">
-        <v>0.01101304554969258</v>
+        <v>0.008740484312195417</v>
       </c>
     </row>
     <row r="83">
@@ -1589,13 +1589,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83" t="n">
-        <v>3.716297626611206</v>
+        <v>3.837287451450706</v>
       </c>
       <c r="C83" t="n">
-        <v>0.6398529339730373</v>
+        <v>0.6469311959062496</v>
       </c>
       <c r="D83" t="n">
-        <v>0.01083982347173043</v>
+        <v>0.00857103966404793</v>
       </c>
     </row>
     <row r="84">
@@ -1603,13 +1603,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84" t="n">
-        <v>3.674169384627332</v>
+        <v>3.811886040018716</v>
       </c>
       <c r="C84" t="n">
-        <v>0.6420253268369371</v>
+        <v>0.6481333589521778</v>
       </c>
       <c r="D84" t="n">
-        <v>0.01063978503956899</v>
+        <v>0.008376026909117226</v>
       </c>
     </row>
     <row r="85">
@@ -1617,13 +1617,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85" t="n">
-        <v>3.632415557851494</v>
+        <v>3.783801604919886</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6443110563138688</v>
+        <v>0.6494823354509084</v>
       </c>
       <c r="D85" t="n">
-        <v>0.01041437317637831</v>
+        <v>0.008157062125581236</v>
       </c>
     </row>
     <row r="86">
@@ -1631,13 +1631,13 @@
         <v>0.84</v>
       </c>
       <c r="B86" t="n">
-        <v>3.591146153441961</v>
+        <v>3.753365295139958</v>
       </c>
       <c r="C86" t="n">
-        <v>0.6466979503548898</v>
+        <v>0.6509680793231909</v>
       </c>
       <c r="D86" t="n">
-        <v>0.01016503080532846</v>
+        <v>0.007915761391617895</v>
       </c>
     </row>
     <row r="87">
@@ -1645,13 +1645,13 @@
         <v>0.85</v>
       </c>
       <c r="B87" t="n">
-        <v>3.550466077354097</v>
+        <v>3.720904248806747</v>
       </c>
       <c r="C87" t="n">
-        <v>0.6491736919649551</v>
+        <v>0.6525805356302103</v>
       </c>
       <c r="D87" t="n">
-        <v>0.009893200849589489</v>
+        <v>0.007653740785405129</v>
       </c>
     </row>
     <row r="88">
@@ -1659,13 +1659,13 @@
         <v>0.86</v>
       </c>
       <c r="B88" t="n">
-        <v>3.510475299507063</v>
+        <v>3.686739846282442</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6517258003066183</v>
+        <v>0.6543096192874591</v>
       </c>
       <c r="D88" t="n">
-        <v>0.009600326232331454</v>
+        <v>0.007372616385120873</v>
       </c>
     </row>
     <row r="89">
@@ -1673,13 +1673,13 @@
         <v>0.87</v>
       </c>
       <c r="B89" t="n">
-        <v>3.471269047997246</v>
+        <v>3.651186226513358</v>
       </c>
       <c r="C89" t="n">
-        <v>0.6543416141928784</v>
+        <v>0.6561451953969066</v>
       </c>
       <c r="D89" t="n">
-        <v>0.009287849876724416</v>
+        <v>0.007074004268943059</v>
       </c>
     </row>
     <row r="90">
@@ -1687,13 +1687,13 @@
         <v>0.88</v>
       </c>
       <c r="B90" t="n">
-        <v>3.432938029841012</v>
+        <v>3.614549062553564</v>
       </c>
       <c r="C90" t="n">
-        <v>0.6570082780202333</v>
+        <v>0.6580770611901402</v>
       </c>
       <c r="D90" t="n">
-        <v>0.008957214705938429</v>
+        <v>0.006759520515049619</v>
       </c>
     </row>
     <row r="91">
@@ -1701,13 +1701,13 @@
         <v>0.89</v>
       </c>
       <c r="B91" t="n">
-        <v>3.395568675904438</v>
+        <v>3.577124589213147</v>
       </c>
       <c r="C91" t="n">
-        <v>0.6597127302015806</v>
+        <v>0.660094929583747</v>
       </c>
       <c r="D91" t="n">
-        <v>0.008609863643143556</v>
+        <v>0.006430781201618484</v>
       </c>
     </row>
     <row r="92">
@@ -1715,13 +1715,13 @@
         <v>0.9</v>
       </c>
       <c r="B92" t="n">
-        <v>3.359243407871393</v>
+        <v>3.539198873381203</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6624416941658366</v>
+        <v>0.6621884143560739</v>
       </c>
       <c r="D92" t="n">
-        <v>0.008247239611509851</v>
+        <v>0.006089402406827588</v>
       </c>
     </row>
     <row r="93">
@@ -1729,13 +1729,13 @@
         <v>0.91</v>
       </c>
       <c r="B93" t="n">
-        <v>3.324040925311048</v>
+        <v>3.501047315721753</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6651816719969729</v>
+        <v>0.6643470169616322</v>
       </c>
       <c r="D93" t="n">
-        <v>0.007870785534207374</v>
+        <v>0.005737000208854861</v>
       </c>
     </row>
     <row r="94">
@@ -1743,13 +1743,13 @@
         <v>0.92</v>
       </c>
       <c r="B94" t="n">
-        <v>3.290036511129422</v>
+        <v>3.462934371112351</v>
       </c>
       <c r="C94" t="n">
-        <v>0.6679189407895472</v>
+        <v>0.6665601150058197</v>
       </c>
       <c r="D94" t="n">
-        <v>0.007481944334406182</v>
+        <v>0.005375190685878237</v>
       </c>
     </row>
     <row r="95">
@@ -1757,13 +1757,13 @@
         <v>0.93</v>
       </c>
       <c r="B95" t="n">
-        <v>3.257302353924969</v>
+        <v>3.425113474358425</v>
       </c>
       <c r="C95" t="n">
-        <v>0.670639551800674</v>
+        <v>0.668816952408289</v>
       </c>
       <c r="D95" t="n">
-        <v>0.007082158935276334</v>
+        <v>0.005005589916075645</v>
       </c>
     </row>
     <row r="96">
@@ -1771,13 +1771,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96" t="n">
-        <v>3.22590788601417</v>
+        <v>3.387827157334678</v>
       </c>
       <c r="C96" t="n">
-        <v>0.6733293324796638</v>
+        <v>0.671106631288208</v>
       </c>
       <c r="D96" t="n">
-        <v>0.006672872259987887</v>
+        <v>0.004629813977625021</v>
       </c>
     </row>
     <row r="97">
@@ -1785,13 +1785,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97" t="n">
-        <v>3.19592013614815</v>
+        <v>3.351307343739174</v>
       </c>
       <c r="C97" t="n">
-        <v>0.6759738914562142</v>
+        <v>0.6734181056087993</v>
       </c>
       <c r="D97" t="n">
-        <v>0.006255527231710897</v>
+        <v>0.004249478948704293</v>
       </c>
     </row>
     <row r="98">
@@ -1799,13 +1799,13 @@
         <v>0.96</v>
       </c>
       <c r="B98" t="n">
-        <v>3.167404096205131</v>
+        <v>3.315775808056176</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6785586265659664</v>
+        <v>0.6757401766218993</v>
       </c>
       <c r="D98" t="n">
-        <v>0.005831566773615431</v>
+        <v>0.0038662009074914</v>
       </c>
     </row>
     <row r="99">
@@ -1813,13 +1813,13 @@
         <v>0.97</v>
       </c>
       <c r="B99" t="n">
-        <v>3.140423101415344</v>
+        <v>3.281444786071448</v>
       </c>
       <c r="C99" t="n">
-        <v>0.6810687359884111</v>
+        <v>0.678061490155821</v>
       </c>
       <c r="D99" t="n">
-        <v>0.005402433808871533</v>
+        <v>0.003481595932164263</v>
       </c>
     </row>
     <row r="100">
@@ -1827,13 +1827,13 @@
         <v>0.98</v>
       </c>
       <c r="B100" t="n">
-        <v>3.115039223955135</v>
+        <v>3.248517725331762</v>
       </c>
       <c r="C100" t="n">
-        <v>0.6834892325664507</v>
+        <v>0.6803705357914991</v>
       </c>
       <c r="D100" t="n">
-        <v>0.00496957126064927</v>
+        <v>0.003097280100900822</v>
       </c>
     </row>
     <row r="101">
@@ -1841,13 +1841,13 @@
         <v>0.99</v>
       </c>
       <c r="B101" t="n">
-        <v>3.091313680035757</v>
+        <v>3.217190165255605</v>
       </c>
       <c r="C101" t="n">
-        <v>0.6858049613693624</v>
+        <v>0.6826556479727315</v>
       </c>
       <c r="D101" t="n">
-        <v>0.004534422052118695</v>
+        <v>0.002714869491879005</v>
       </c>
     </row>
     <row r="102">
@@ -1855,13 +1855,13 @@
         <v>1</v>
       </c>
       <c r="B102" t="n">
-        <v>3.069307250910638</v>
+        <v>3.187650738155787</v>
       </c>
       <c r="C102" t="n">
-        <v>0.6880006205513994</v>
+        <v>0.6849050090962523</v>
       </c>
       <c r="D102" t="n">
-        <v>0.004098429106449869</v>
+        <v>0.002335980183276748</v>
       </c>
     </row>
     <row r="103">
@@ -1869,13 +1869,13 @@
         <v>1.01</v>
       </c>
       <c r="B103" t="n">
-        <v>3.049080718534082</v>
+        <v>3.16008228420345</v>
       </c>
       <c r="C103" t="n">
-        <v>0.6900607855467809</v>
+        <v>0.6871066546263742</v>
       </c>
       <c r="D103" t="n">
-        <v>0.003663035346812847</v>
+        <v>0.001962228253271978</v>
       </c>
     </row>
     <row r="104">
@@ -1883,13 +1883,13 @@
         <v>1.02</v>
       </c>
       <c r="B104" t="n">
-        <v>3.030695316926193</v>
+        <v>3.134663075329755</v>
       </c>
       <c r="C104" t="n">
-        <v>0.6919699366283292</v>
+        <v>0.6892484802769688</v>
       </c>
       <c r="D104" t="n">
-        <v>0.003229683696377692</v>
+        <v>0.001595229780042631</v>
       </c>
     </row>
     <row r="105">
@@ -1897,13 +1897,13 @@
         <v>1.03</v>
       </c>
       <c r="B105" t="n">
-        <v>3.014213200635465</v>
+        <v>3.111568145216009</v>
       </c>
       <c r="C105" t="n">
-        <v>0.6937124898415032</v>
+        <v>0.6913182513006015</v>
       </c>
       <c r="D105" t="n">
-        <v>0.002799817078314459</v>
+        <v>0.001236600841766637</v>
       </c>
     </row>
     <row r="106">
@@ -1911,13 +1911,13 @@
         <v>1.04</v>
       </c>
       <c r="B106" t="n">
-        <v>2.999697932044969</v>
+        <v>3.090970724862362</v>
       </c>
       <c r="C106" t="n">
-        <v>0.6952728313080502</v>
+        <v>0.6933036139206611</v>
       </c>
       <c r="D106" t="n">
-        <v>0.002374878415793203</v>
+        <v>0.0008879575166219292</v>
       </c>
     </row>
     <row r="107">
@@ -1925,13 +1925,13 @@
         <v>1.05</v>
       </c>
       <c r="B107" t="n">
-        <v>2.987214989643348</v>
+        <v>3.073043785754999</v>
       </c>
       <c r="C107" t="n">
-        <v>0.6966353548739872</v>
+        <v>0.6951921089373131</v>
       </c>
       <c r="D107" t="n">
-        <v>0.001956310631983989</v>
+        <v>0.0005509158827864393</v>
       </c>
     </row>
     <row r="108">
@@ -1939,13 +1939,13 @@
         <v>1.06</v>
       </c>
       <c r="B108" t="n">
-        <v>2.97683229978231</v>
+        <v>3.057961695386162</v>
       </c>
       <c r="C108" t="n">
-        <v>0.6977845030551709</v>
+        <v>0.6969711875320347</v>
       </c>
       <c r="D108" t="n">
-        <v>0.001545556650056867</v>
+        <v>0.0002270920184380999</v>
       </c>
     </row>
     <row r="109">
@@ -1953,13 +1953,13 @@
         <v>1.07</v>
       </c>
       <c r="B109" t="n">
-        <v>2.968620794872124</v>
+        <v>3.045901992844426</v>
       </c>
       <c r="C109" t="n">
-        <v>0.6987048112103807</v>
+        <v>0.6986282292883392</v>
       </c>
       <c r="D109" t="n">
-        <v>0.001144059393181898</v>
+        <v>-8.189799824516279e-05</v>
       </c>
     </row>
     <row r="110">
@@ -1967,13 +1967,13 @@
         <v>1.08</v>
       </c>
       <c r="B110" t="n">
-        <v>2.962655001431464</v>
+        <v>3.037047295419077</v>
       </c>
       <c r="C110" t="n">
-        <v>0.699380954846743</v>
+        <v>0.7001505624380776</v>
       </c>
       <c r="D110" t="n">
-        <v>0.0007532617845291412</v>
+        <v>-0.0003744380890854035</v>
       </c>
     </row>
     <row r="111">
@@ -1981,13 +1981,13 @@
         <v>1.09</v>
       </c>
       <c r="B111" t="n">
-        <v>2.959013661913793</v>
+        <v>3.031587350698613</v>
       </c>
       <c r="C111" t="n">
-        <v>0.6997977999355575</v>
+        <v>0.7015254863333917</v>
       </c>
       <c r="D111" t="n">
-        <v>0.0003746067472686545</v>
+        <v>-0.0006489121759047038</v>
       </c>
     </row>
     <row r="112">
@@ -1995,13 +1995,13 @@
         <v>1.1</v>
       </c>
       <c r="B112" t="n">
-        <v>2.957780394786506</v>
+        <v>3.029721252549284</v>
       </c>
       <c r="C112" t="n">
-        <v>0.6999404560883336</v>
+        <v>0.7027402961340202</v>
       </c>
       <c r="D112" t="n">
-        <v>9.537204570494757e-06</v>
+        <v>-0.0009037041805251279</v>
       </c>
     </row>
     <row r="113">
@@ -2009,13 +2009,13 @@
         <v>1.11</v>
       </c>
       <c r="B113" t="n">
-        <v>2.958040384433255</v>
+        <v>3.029815745696556</v>
       </c>
       <c r="C113" t="n">
-        <v>0.6999411064425041</v>
+        <v>0.7038552667079047</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.0003578621561182056</v>
+        <v>-0.001150830613997983</v>
       </c>
     </row>
     <row r="114">
@@ -2023,13 +2023,13 @@
         <v>1.12</v>
       </c>
       <c r="B114" t="n">
-        <v>2.958806432715411</v>
+        <v>3.030094134530496</v>
       </c>
       <c r="C114" t="n">
-        <v>0.6999417181098533</v>
+        <v>0.7049398424544919</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.0007437560827318656</v>
+        <v>-0.001403106546589467</v>
       </c>
     </row>
     <row r="115">
@@ -2037,13 +2037,13 @@
         <v>1.13</v>
       </c>
       <c r="B115" t="n">
-        <v>2.960057837175289</v>
+        <v>3.030548806152325</v>
       </c>
       <c r="C115" t="n">
-        <v>0.6999422926538972</v>
+        <v>0.7059950941578114</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.001147075805172756</v>
+        <v>-0.001660113738943973</v>
       </c>
     </row>
     <row r="116">
@@ -2051,13 +2051,13 @@
         <v>1.14</v>
       </c>
       <c r="B116" t="n">
-        <v>2.96177410560606</v>
+        <v>3.031172174742411</v>
       </c>
       <c r="C116" t="n">
-        <v>0.6999428316381631</v>
+        <v>0.7070221036306962</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.001566752553343148</v>
+        <v>-0.001921433951705897</v>
       </c>
     </row>
     <row r="117">
@@ -2065,13 +2065,13 @@
         <v>1.15</v>
       </c>
       <c r="B117" t="n">
-        <v>2.963934922667274</v>
+        <v>3.031956677220111</v>
       </c>
       <c r="C117" t="n">
-        <v>0.6999433366261886</v>
+        <v>0.7080219632471142</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.002001717557145312</v>
+        <v>-0.002186648945519633</v>
       </c>
     </row>
     <row r="118">
@@ -2079,13 +2079,13 @@
         <v>1.16</v>
       </c>
       <c r="B118" t="n">
-        <v>2.966520118077639</v>
+        <v>3.032894769100779</v>
       </c>
       <c r="C118" t="n">
-        <v>0.6999438091815211</v>
+        <v>0.7089957754903251</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.00245090204648151</v>
+        <v>-0.00245534048102957</v>
       </c>
     </row>
     <row r="119">
@@ -2093,13 +2093,13 @@
         <v>1.17</v>
       </c>
       <c r="B119" t="n">
-        <v>2.969509636339483</v>
+        <v>3.033978920547809</v>
       </c>
       <c r="C119" t="n">
-        <v>0.6999442508677166</v>
+        <v>0.7099446525172666</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.002913237251254031</v>
+        <v>-0.002727090318880114</v>
       </c>
     </row>
     <row r="120">
@@ -2107,13 +2107,13 @@
         <v>1.18</v>
       </c>
       <c r="B120" t="n">
-        <v>2.972883507955506</v>
+        <v>3.035201612617933</v>
       </c>
       <c r="C120" t="n">
-        <v>0.6999446632483396</v>
+        <v>0.710869715739552</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.003387654401365136</v>
+        <v>-0.003001480219715654</v>
       </c>
     </row>
     <row r="121">
@@ -2121,13 +2121,13 @@
         <v>1.19</v>
       </c>
       <c r="B121" t="n">
-        <v>2.976621822104333</v>
+        <v>3.036555333698213</v>
       </c>
       <c r="C121" t="n">
-        <v>0.6999450478869618</v>
+        <v>0.7117720954214416</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.003873084726717098</v>
+        <v>-0.003278091944180585</v>
       </c>
     </row>
     <row r="122">
@@ -2135,13 +2135,13 @@
         <v>1.2</v>
       </c>
       <c r="B122" t="n">
-        <v>2.980704700746943</v>
+        <v>3.038032576133471</v>
       </c>
       <c r="C122" t="n">
-        <v>0.6999454063471618</v>
+        <v>0.7126529302951325</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.004368459457212186</v>
+        <v>-0.003556507252919301</v>
       </c>
     </row>
     <row r="123">
@@ -2149,13 +2149,13 @@
         <v>1.21</v>
       </c>
       <c r="B123" t="n">
-        <v>2.98511227414127</v>
+        <v>3.039625833043093</v>
       </c>
       <c r="C123" t="n">
-        <v>0.6999457401925249</v>
+        <v>0.7135133671936946</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.004872709822752672</v>
+        <v>-0.003836307906576198</v>
       </c>
     </row>
     <row r="124">
@@ -2163,13 +2163,13 @@
         <v>1.22</v>
       </c>
       <c r="B124" t="n">
-        <v>2.989824657747222</v>
+        <v>3.041327595326437</v>
       </c>
       <c r="C124" t="n">
-        <v>0.6999460509866413</v>
+        <v>0.7143545607019578</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.005384767053240826</v>
+        <v>-0.004117075665795668</v>
       </c>
     </row>
     <row r="125">
@@ -2177,13 +2177,13 @@
         <v>1.23</v>
       </c>
       <c r="B125" t="n">
-        <v>2.994821930509029</v>
+        <v>3.043130348856223</v>
       </c>
       <c r="C125" t="n">
-        <v>0.6999463402931071</v>
+        <v>0.7151776728256474</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.005903562378578919</v>
+        <v>-0.004398392291222109</v>
       </c>
     </row>
     <row r="126">
@@ -2191,13 +2191,13 @@
         <v>1.24</v>
       </c>
       <c r="B126" t="n">
-        <v>3.000084114506171</v>
+        <v>3.045026571859554</v>
       </c>
       <c r="C126" t="n">
-        <v>0.6999466096755228</v>
+        <v>0.7159838726790402</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.006428027028669223</v>
+        <v>-0.004679839543499914</v>
       </c>
     </row>
     <row r="127">
@@ -2205,13 +2205,13 @@
         <v>1.25</v>
       </c>
       <c r="B127" t="n">
-        <v>3.005591155968255</v>
+        <v>3.047008732486345</v>
       </c>
       <c r="C127" t="n">
-        <v>0.6999468606974929</v>
+        <v>0.7167743361914056</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.006957092233414007</v>
+        <v>-0.004960999183273478</v>
       </c>
     </row>
     <row r="128">
@@ -2219,13 +2219,13 @@
         <v>1.26</v>
       </c>
       <c r="B128" t="n">
-        <v>3.011322907653036</v>
+        <v>3.049069286565172</v>
       </c>
       <c r="C128" t="n">
-        <v>0.6999470949226259</v>
+        <v>0.7175502458324768</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.007489689222715543</v>
+        <v>-0.005241452971187194</v>
       </c>
     </row>
     <row r="129">
@@ -2233,13 +2233,13 @@
         <v>1.27</v>
       </c>
       <c r="B129" t="n">
-        <v>3.017259112590311</v>
+        <v>3.051200675546667</v>
       </c>
       <c r="C129" t="n">
-        <v>0.6999473139145337</v>
+        <v>0.7183127903571882</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.008024749226476099</v>
+        <v>-0.005520782667885458</v>
       </c>
     </row>
     <row r="130">
@@ -2247,13 +2247,13 @@
         <v>1.28</v>
       </c>
       <c r="B130" t="n">
-        <v>3.023379389197728</v>
+        <v>3.053395324634769</v>
       </c>
       <c r="C130" t="n">
-        <v>0.6999475192368311</v>
+        <v>0.7190631645698979</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.008561203474597953</v>
+        <v>-0.005798570034012665</v>
       </c>
     </row>
     <row r="131">
@@ -2261,13 +2261,13 @@
         <v>1.29</v>
       </c>
       <c r="B131" t="n">
-        <v>3.029663217777584</v>
+        <v>3.055645641106272</v>
       </c>
       <c r="C131" t="n">
-        <v>0.6999477124531356</v>
+        <v>0.719802569108309</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.009097983196983371</v>
+        <v>-0.00607439683021321</v>
       </c>
     </row>
     <row r="132">
@@ -2275,13 +2275,13 @@
         <v>1.3</v>
       </c>
       <c r="B132" t="n">
-        <v>3.03608992840642</v>
+        <v>3.05794401281922</v>
       </c>
       <c r="C132" t="n">
-        <v>0.6999478951270672</v>
+        <v>0.7205322102472841</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.009634019623534622</v>
+        <v>-0.006347844817131487</v>
       </c>
     </row>
     <row r="133">
@@ -2289,13 +2289,13 @@
         <v>1.31</v>
       </c>
       <c r="B133" t="n">
-        <v>3.042638690231771</v>
+        <v>3.060282806910823</v>
       </c>
       <c r="C133" t="n">
-        <v>0.699948068822248</v>
+        <v>0.7212532997227475</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.01016824398415398</v>
+        <v>-0.006618495755411889</v>
       </c>
     </row>
     <row r="134">
@@ -2303,13 +2303,13 @@
         <v>1.32</v>
       </c>
       <c r="B134" t="n">
-        <v>3.049288502192597</v>
+        <v>3.062654368685681</v>
       </c>
       <c r="C134" t="n">
-        <v>0.6999482351023022</v>
+        <v>0.7219670545758521</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.01069958750874371</v>
+        <v>-0.006885931405698814</v>
       </c>
     </row>
     <row r="135">
@@ -2317,13 +2317,13 @@
         <v>1.33</v>
       </c>
       <c r="B135" t="n">
-        <v>3.056018185181936</v>
+        <v>3.06505102069515</v>
       </c>
       <c r="C135" t="n">
-        <v>0.6999483955308554</v>
+        <v>0.7226746970175847</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.0112269814272061</v>
+        <v>-0.007149733528636654</v>
       </c>
     </row>
     <row r="136">
@@ -2331,13 +2331,13 @@
         <v>1.34</v>
       </c>
       <c r="B136" t="n">
-        <v>3.062806375671963</v>
+        <v>3.067465062008794</v>
       </c>
       <c r="C136" t="n">
-        <v>0.6999485516715351</v>
+        <v>0.7233774543139773</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.0117493569694434</v>
+        <v>-0.007409483884869804</v>
       </c>
     </row>
     <row r="137">
@@ -2345,13 +2345,13 @@
         <v>1.35</v>
       </c>
       <c r="B137" t="n">
-        <v>3.069631520823056</v>
+        <v>3.069888767678892</v>
       </c>
       <c r="C137" t="n">
-        <v>0.6999487050879704</v>
+        <v>0.7240765586920809</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.01226564536535789</v>
+        <v>-0.007664764235042661</v>
       </c>
     </row>
     <row r="138">
@@ -2359,13 +2359,13 @@
         <v>1.36</v>
       </c>
       <c r="B138" t="n">
-        <v>3.076471875099579</v>
+        <v>3.072314388399059</v>
       </c>
       <c r="C138" t="n">
-        <v>0.6999488573437913</v>
+        <v>0.7247732472668603</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.01277477784485184</v>
+        <v>-0.007915156339799617</v>
       </c>
     </row>
     <row r="139">
@@ -2373,13 +2373,13 @@
         <v>1.37</v>
       </c>
       <c r="B139" t="n">
-        <v>3.083305498415909</v>
+        <v>3.074734150358001</v>
       </c>
       <c r="C139" t="n">
-        <v>0.69994901000263</v>
+        <v>0.7254687619891581</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.01327568563782753</v>
+        <v>-0.008160241959785066</v>
       </c>
     </row>
     <row r="140">
@@ -2387,13 +2387,13 @@
         <v>1.38</v>
       </c>
       <c r="B140" t="n">
-        <v>3.090110255836764</v>
+        <v>3.077140255289523</v>
       </c>
       <c r="C140" t="n">
-        <v>0.6999491646281191</v>
+        <v>0.7261643496148756</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.01376729997418721</v>
+        <v>-0.008399602855643406</v>
       </c>
     </row>
     <row r="141">
@@ -2401,13 +2401,13 @@
         <v>1.39</v>
       </c>
       <c r="B141" t="n">
-        <v>3.096863818856095</v>
+        <v>3.07952488071984</v>
       </c>
       <c r="C141" t="n">
-        <v>0.6999493227838934</v>
+        <v>0.7268612616955203</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.01424855208383317</v>
+        <v>-0.008632820788019031</v>
       </c>
     </row>
     <row r="142">
@@ -2415,13 +2415,13 @@
         <v>1.4</v>
       </c>
       <c r="B142" t="n">
-        <v>3.103543668278698</v>
+        <v>3.081880180413287</v>
       </c>
       <c r="C142" t="n">
-        <v>0.6999494860335888</v>
+        <v>0.7275607545902586</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.01471837319666767</v>
+        <v>-0.008859477517556334</v>
       </c>
     </row>
     <row r="143">
@@ -2429,13 +2429,13 @@
         <v>1.41</v>
       </c>
       <c r="B143" t="n">
-        <v>3.110127098728309</v>
+        <v>3.084198285017456</v>
       </c>
       <c r="C143" t="n">
-        <v>0.6999496559408426</v>
+        <v>0.7282640894996248</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.01517569454259298</v>
+        <v>-0.009079154804899703</v>
       </c>
     </row>
     <row r="144">
@@ -2443,13 +2443,13 @@
         <v>1.42</v>
       </c>
       <c r="B144" t="n">
-        <v>3.116591224805175</v>
+        <v>3.086471302908772</v>
       </c>
       <c r="C144" t="n">
-        <v>0.699949834069294</v>
+        <v>0.7289725325210282</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.01561944735151138</v>
+        <v>-0.009291434410693543</v>
       </c>
     </row>
     <row r="145">
@@ -2457,13 +2457,13 @@
         <v>1.43</v>
       </c>
       <c r="B145" t="n">
-        <v>3.122912988915014</v>
+        <v>3.08869132123948</v>
       </c>
       <c r="C145" t="n">
-        <v>0.6999500219825842</v>
+        <v>0.7296873547262088</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.01604856285332514</v>
+        <v>-0.00949589809558225</v>
       </c>
     </row>
     <row r="146">
@@ -2471,13 +2471,13 @@
         <v>1.44</v>
       </c>
       <c r="B146" t="n">
-        <v>3.129069170789885</v>
+        <v>3.090850407186898</v>
       </c>
       <c r="C146" t="n">
-        <v>0.6999502212443561</v>
+        <v>0.7304098322607919</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.01646197227793653</v>
+        <v>-0.009692127620210215</v>
       </c>
     </row>
     <row r="147">
@@ -2485,13 +2485,13 @@
         <v>1.45</v>
       </c>
       <c r="B147" t="n">
-        <v>3.135036398719691</v>
+        <v>3.092940609405773</v>
       </c>
       <c r="C147" t="n">
-        <v>0.6999504334182551</v>
+        <v>0.7311412464660976</v>
       </c>
       <c r="D147" t="n">
-        <v>-0.01685860685524781</v>
+        <v>-0.009879704745221828</v>
       </c>
     </row>
     <row r="148">
@@ -2499,13 +2499,13 @@
         <v>1.46</v>
       </c>
       <c r="B148" t="n">
-        <v>3.14079116251095</v>
+        <v>3.094953959684429</v>
       </c>
       <c r="C148" t="n">
-        <v>0.6999506600679292</v>
+        <v>0.7318828840233672</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.01723739781516126</v>
+        <v>-0.01005821123126149</v>
       </c>
     </row>
     <row r="149">
@@ -2513,13 +2513,13 @@
         <v>1.47</v>
       </c>
       <c r="B149" t="n">
-        <v>3.146309828186982</v>
+        <v>3.096882474805317</v>
       </c>
       <c r="C149" t="n">
-        <v>0.699950902757029</v>
+        <v>0.7326360371205721</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.01759727638757916</v>
+        <v>-0.01022722883897359</v>
       </c>
     </row>
     <row r="150">
@@ -2527,13 +2527,13 @@
         <v>1.48</v>
       </c>
       <c r="B150" t="n">
-        <v>3.151568654440844</v>
+        <v>3.098718158610432</v>
       </c>
       <c r="C150" t="n">
-        <v>0.6999511630492086</v>
+        <v>0.7334020036419827</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.01793717380240376</v>
+        <v>-0.01038633932900253</v>
       </c>
     </row>
     <row r="151">
@@ -2541,13 +2541,13 @@
         <v>1.49</v>
       </c>
       <c r="B151" t="n">
-        <v>3.156543810849155</v>
+        <v>3.100453004271931</v>
       </c>
       <c r="C151" t="n">
-        <v>0.6999514425081255</v>
+        <v>0.7341820873806789</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.01825602128953735</v>
+        <v>-0.01053512446199269</v>
       </c>
     </row>
     <row r="152">
@@ -2555,13 +2555,13 @@
         <v>1.5</v>
       </c>
       <c r="B152" t="n">
-        <v>3.161211397851396</v>
+        <v>3.102078996768135</v>
       </c>
       <c r="C152" t="n">
-        <v>0.6999517426974412</v>
+        <v>0.7349775982741976</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.01855275007888219</v>
+        <v>-0.01067316599858849</v>
       </c>
     </row>
     <row r="153">
@@ -2569,13 +2569,13 @@
         <v>1.51</v>
       </c>
       <c r="B153" t="n">
-        <v>3.165547468495378</v>
+        <v>3.103588115564914</v>
       </c>
       <c r="C153" t="n">
-        <v>0.6999520651808216</v>
+        <v>0.7357898526635214</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.01882629140034055</v>
+        <v>-0.0108000456994343</v>
       </c>
     </row>
     <row r="154">
@@ -2583,13 +2583,13 @@
         <v>1.52</v>
       </c>
       <c r="B154" t="n">
-        <v>3.169528051945282</v>
+        <v>3.104972337502292</v>
       </c>
       <c r="C154" t="n">
-        <v>0.6999524115219379</v>
+        <v>0.736620173575624</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.01907557648381471</v>
+        <v>-0.01091534532517453</v>
       </c>
     </row>
     <row r="155">
@@ -2597,13 +2597,13 @@
         <v>1.53</v>
       </c>
       <c r="B155" t="n">
-        <v>3.173129178744058</v>
+        <v>3.106223639885873</v>
       </c>
       <c r="C155" t="n">
-        <v>0.6999527832844662</v>
+        <v>0.7374698910298049</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.01929953655920693</v>
+        <v>-0.01101864663645357</v>
       </c>
     </row>
     <row r="156">
@@ -2611,13 +2611,13 @@
         <v>1.54</v>
       </c>
       <c r="B156" t="n">
-        <v>3.176326907817</v>
+        <v>3.107334003782534</v>
       </c>
       <c r="C156" t="n">
-        <v>0.6999531820320888</v>
+        <v>0.7383403423680555</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.01949710285641949</v>
+        <v>-0.01110953139391581</v>
       </c>
     </row>
     <row r="157">
@@ -2625,13 +2625,13 @@
         <v>1.55</v>
       </c>
       <c r="B157" t="n">
-        <v>3.179097355197983</v>
+        <v>3.108295417519536</v>
       </c>
       <c r="C157" t="n">
-        <v>0.6999536093284945</v>
+        <v>0.7392328726097186</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.01966720660535465</v>
+        <v>-0.01118758135820564</v>
       </c>
     </row>
     <row r="158">
@@ -2639,13 +2639,13 @@
         <v>1.56</v>
       </c>
       <c r="B158" t="n">
-        <v>3.181416724454189</v>
+        <v>3.109099880386009</v>
       </c>
       <c r="C158" t="n">
-        <v>0.6999540667373795</v>
+        <v>0.740148834830718</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.01980877903591469</v>
+        <v>-0.01125237828996747</v>
       </c>
     </row>
     <row r="159">
@@ -2653,13 +2653,13 @@
         <v>1.57</v>
       </c>
       <c r="B159" t="n">
-        <v>3.183261338779199</v>
+        <v>3.109739406535509</v>
       </c>
       <c r="C159" t="n">
-        <v>0.6999545558224477</v>
+        <v>0.7410895905676537</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.01992075137800188</v>
+        <v>-0.01130350394984569</v>
       </c>
     </row>
     <row r="160">
@@ -2667,13 +2667,13 @@
         <v>1.58</v>
       </c>
       <c r="B160" t="n">
-        <v>3.184607674717995</v>
+        <v>3.110206029088031</v>
       </c>
       <c r="C160" t="n">
-        <v>0.6999550781474115</v>
+        <v>0.7420565102470774</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.02000205486151849</v>
+        <v>-0.01134054009848469</v>
       </c>
     </row>
     <row r="161">
@@ -2681,13 +2681,13 @@
         <v>1.59</v>
       </c>
       <c r="B161" t="n">
-        <v>3.185432397480874</v>
+        <v>3.110491804429645</v>
       </c>
       <c r="C161" t="n">
-        <v>0.6999556352759925</v>
+        <v>0.7430509736402857</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.0200516207163668</v>
+        <v>-0.01136306849652887</v>
       </c>
     </row>
     <row r="162">
@@ -2695,13 +2695,13 @@
         <v>1.6</v>
       </c>
       <c r="B162" t="n">
-        <v>3.185712397796389</v>
+        <v>3.110588816707562</v>
       </c>
       <c r="C162" t="n">
-        <v>0.6999562287719225</v>
+        <v>0.744074370343986</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.02006838017244906</v>
+        <v>-0.01137067090462262</v>
       </c>
     </row>
     <row r="163">
@@ -2709,13 +2709,13 @@
         <v>1.61</v>
       </c>
       <c r="B163" t="n">
-        <v>3.185485823814443</v>
+        <v>3.110306829736162</v>
       </c>
       <c r="C163" t="n">
-        <v>0.6999846919401748</v>
+        <v>0.7451194290248024</v>
       </c>
       <c r="D163" t="n">
-        <v>-0.02006386785654099</v>
+        <v>-0.01137063842334133</v>
       </c>
     </row>
     <row r="164">
@@ -2723,13 +2723,13 @@
         <v>1.62</v>
       </c>
       <c r="B164" t="n">
-        <v>3.1848089618109</v>
+        <v>3.109466239672047</v>
       </c>
       <c r="C164" t="n">
-        <v>0.7000682805663967</v>
+        <v>0.7461779349674252</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.02005025721560123</v>
+        <v>-0.01137045397833707</v>
       </c>
     </row>
     <row r="165">
@@ -2737,13 +2737,13 @@
         <v>1.63</v>
       </c>
       <c r="B165" t="n">
-        <v>3.183686242250578</v>
+        <v>3.108075322135045</v>
       </c>
       <c r="C165" t="n">
-        <v>0.7002061393912417</v>
+        <v>0.7472498706081262</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.02002743770980643</v>
+        <v>-0.01136998706786927</v>
       </c>
     </row>
     <row r="166">
@@ -2751,13 +2751,13 @@
         <v>1.64</v>
       </c>
       <c r="B166" t="n">
-        <v>3.182122278165313</v>
+        <v>3.106142633715707</v>
       </c>
       <c r="C166" t="n">
-        <v>0.7003974252245444</v>
+        <v>0.7483352186990856</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.01999529879933329</v>
+        <v>-0.01136910719019734</v>
       </c>
     </row>
     <row r="167">
@@ -2765,13 +2765,13 @@
         <v>1.65</v>
       </c>
       <c r="B167" t="n">
-        <v>3.180121859055396</v>
+        <v>3.103676997590727</v>
       </c>
       <c r="C167" t="n">
-        <v>0.7006413062845553</v>
+        <v>0.7494339623001252</v>
       </c>
       <c r="D167" t="n">
-        <v>-0.01995372994435845</v>
+        <v>-0.01136768384358072</v>
       </c>
     </row>
     <row r="168">
@@ -2779,13 +2779,13 @@
         <v>1.66</v>
       </c>
       <c r="B168" t="n">
-        <v>3.177689944732306</v>
+        <v>3.100687489131924</v>
       </c>
       <c r="C168" t="n">
-        <v>0.7009369615518379</v>
+        <v>0.7505460847704694</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.01990262060505858</v>
+        <v>-0.01136558652627883</v>
       </c>
     </row>
     <row r="169">
@@ -2793,13 +2793,13 @@
         <v>1.67</v>
       </c>
       <c r="B169" t="n">
-        <v>3.17483165911127</v>
+        <v>3.097183421533567</v>
       </c>
       <c r="C169" t="n">
-        <v>0.7012835801373333</v>
+        <v>0.7516715697605352</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.01984186024161037</v>
+        <v>-0.01136268473655109</v>
       </c>
     </row>
     <row r="170">
@@ -2807,13 +2807,13 @@
         <v>1.68</v>
       </c>
       <c r="B170" t="n">
-        <v>3.17155228396203</v>
+        <v>3.093174331481992</v>
       </c>
       <c r="C170" t="n">
-        <v>0.7016803606641191</v>
+        <v>0.7528104012037471</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.01977133831419046</v>
+        <v>-0.01135884797265692</v>
       </c>
     </row>
     <row r="171">
@@ -2821,13 +2821,13 @@
         <v>1.69</v>
       </c>
       <c r="B171" t="n">
-        <v>3.167857252626069</v>
+        <v>3.088669964890628</v>
       </c>
       <c r="C171" t="n">
-        <v>0.7021265106624135</v>
+        <v>0.7539625633083775</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.01969094428297554</v>
+        <v>-0.01135394573285575</v>
       </c>
     </row>
     <row r="172">
@@ -2835,13 +2835,13 @@
         <v>1.7</v>
       </c>
       <c r="B172" t="n">
-        <v>3.163752143708406</v>
+        <v>3.083680262722698</v>
       </c>
       <c r="C172" t="n">
-        <v>0.7026212459773952</v>
+        <v>0.7551280405494123</v>
       </c>
       <c r="D172" t="n">
-        <v>-0.01960056760814227</v>
+        <v>-0.011347847515407</v>
       </c>
     </row>
     <row r="173">
@@ -2849,13 +2849,13 @@
         <v>1.71</v>
       </c>
       <c r="B173" t="n">
-        <v>3.159242674751905</v>
+        <v>3.078215346923006</v>
       </c>
       <c r="C173" t="n">
-        <v>0.7031637901894361</v>
+        <v>0.7563068176604376</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.01950009774986731</v>
+        <v>-0.01134042281857009</v>
       </c>
     </row>
     <row r="174">
@@ -2863,13 +2863,13 @@
         <v>1.72</v>
       </c>
       <c r="B174" t="n">
-        <v>3.154334695901876</v>
+        <v>3.072285506479272</v>
       </c>
       <c r="C174" t="n">
-        <v>0.7037533740463621</v>
+        <v>0.7574988796255497</v>
       </c>
       <c r="D174" t="n">
-        <v>-0.01938942416832734</v>
+        <v>-0.01133154114060446</v>
       </c>
     </row>
     <row r="175">
@@ -2877,13 +2877,13 @@
         <v>1.73</v>
       </c>
       <c r="B175" t="n">
-        <v>3.149034183568597</v>
+        <v>3.065901183632619</v>
       </c>
       <c r="C175" t="n">
-        <v>0.7043892349073775</v>
+        <v>0.7587042116712863</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.01926843632369902</v>
+        <v>-0.01132107197976951</v>
       </c>
     </row>
     <row r="176">
@@ -2891,13 +2891,13 @@
         <v>1.74</v>
       </c>
       <c r="B176" t="n">
-        <v>3.143347234095168</v>
+        <v>3.059072960255836</v>
       </c>
       <c r="C176" t="n">
-        <v>0.7050706161983112</v>
+        <v>0.7599227992585751</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.01913702367615902</v>
+        <v>-0.01130888483432469</v>
       </c>
     </row>
     <row r="177">
@@ -2905,13 +2905,13 @@
         <v>1.75</v>
       </c>
       <c r="B177" t="n">
-        <v>3.137280057437944</v>
+        <v>3.051811544417146</v>
       </c>
       <c r="C177" t="n">
-        <v>0.7057967668778592</v>
+        <v>0.7611546280747042</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.01899507568588401</v>
+        <v>-0.0112948492025294</v>
       </c>
     </row>
     <row r="178">
@@ -2919,13 +2919,13 @@
         <v>1.76</v>
       </c>
       <c r="B178" t="n">
-        <v>3.130838970866598</v>
+        <v>3.044127757146228</v>
       </c>
       <c r="C178" t="n">
-        <v>0.7065669409145192</v>
+        <v>0.7623996840253078</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.01884248181305065</v>
+        <v>-0.01127883458264308</v>
       </c>
     </row>
     <row r="179">
@@ -2933,13 +2933,13 @@
         <v>1.77</v>
       </c>
       <c r="B179" t="n">
-        <v>3.124030392690649</v>
+        <v>3.036032519418308</v>
       </c>
       <c r="C179" t="n">
-        <v>0.7073803967739297</v>
+        <v>0.7636579532263702</v>
       </c>
       <c r="D179" t="n">
-        <v>-0.01867913151783562</v>
+        <v>-0.01126071047292514</v>
       </c>
     </row>
     <row r="180">
@@ -2947,13 +2947,13 @@
         <v>1.78</v>
       </c>
       <c r="B180" t="n">
-        <v>3.116860836019085</v>
+        <v>3.027536839371173</v>
       </c>
       <c r="C180" t="n">
-        <v>0.7082363969163463</v>
+        <v>0.7649294219962447</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.01850491426041559</v>
+        <v>-0.01124034637163501</v>
       </c>
     </row>
     <row r="181">
@@ -2961,13 +2961,13 @@
         <v>1.79</v>
       </c>
       <c r="B181" t="n">
-        <v>3.109336902559532</v>
+        <v>3.018651799769032</v>
       </c>
       <c r="C181" t="n">
-        <v>0.7091342073040007</v>
+        <v>0.7662140768476868</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.01831971950096721</v>
+        <v>-0.01121761177703212</v>
       </c>
     </row>
     <row r="182">
@@ -2975,13 +2975,13 @@
         <v>1.8</v>
       </c>
       <c r="B182" t="n">
-        <v>3.101465276463135</v>
+        <v>3.009388545726148</v>
       </c>
       <c r="C182" t="n">
-        <v>0.7100730969181114</v>
+        <v>0.7675119044799033</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.01812343669966716</v>
+        <v>-0.01119237618737589</v>
       </c>
     </row>
     <row r="183">
@@ -2989,13 +2989,13 @@
         <v>1.81</v>
       </c>
       <c r="B183" t="n">
-        <v>3.093252718221173</v>
+        <v>2.999758272702289</v>
       </c>
       <c r="C183" t="n">
-        <v>0.7110523372853251</v>
+        <v>0.7688228917706112</v>
       </c>
       <c r="D183" t="n">
-        <v>-0.01791595531669211</v>
+        <v>-0.01116450910092574</v>
       </c>
     </row>
     <row r="184">
@@ -3003,13 +3003,13 @@
         <v>1.82</v>
       </c>
       <c r="B184" t="n">
-        <v>3.084706058619143</v>
+        <v>2.989772214781055</v>
       </c>
       <c r="C184" t="n">
-        <v>0.712071202013389</v>
+        <v>0.7701470257681114</v>
       </c>
       <c r="D184" t="n">
-        <v>-0.01769716481221872</v>
+        <v>-0.01113388001594109</v>
       </c>
     </row>
     <row r="185">
@@ -3017,13 +3017,13 @@
         <v>1.83</v>
       </c>
       <c r="B185" t="n">
-        <v>3.075832192753862</v>
+        <v>2.979441633241248</v>
       </c>
       <c r="C185" t="n">
-        <v>0.713128966335865</v>
+        <v>0.7714842936833716</v>
       </c>
       <c r="D185" t="n">
-        <v>-0.01746695464642366</v>
+        <v>-0.01110035843068137</v>
       </c>
     </row>
     <row r="186">
@@ -3031,13 +3031,13 @@
         <v>1.84</v>
       </c>
       <c r="B186" t="n">
-        <v>3.066638074118885</v>
+        <v>2.968777805430522</v>
       </c>
       <c r="C186" t="n">
-        <v>0.7142249066657183</v>
+        <v>0.7728346828821197</v>
       </c>
       <c r="D186" t="n">
-        <v>-0.0172252142794836</v>
+        <v>-0.01106381384340601</v>
       </c>
     </row>
     <row r="187">
@@ -3045,13 +3045,13 @@
         <v>1.85</v>
       </c>
       <c r="B187" t="n">
-        <v>3.057130708763303</v>
+        <v>2.957792013949649</v>
       </c>
       <c r="C187" t="n">
-        <v>0.7153583001576215</v>
+        <v>0.7741981808769475</v>
       </c>
       <c r="D187" t="n">
-        <v>-0.01697183317157521</v>
+        <v>-0.01102411575237442</v>
       </c>
     </row>
     <row r="188">
@@ -3059,13 +3059,13 @@
         <v>1.86</v>
       </c>
       <c r="B188" t="n">
-        <v>3.047317149528781</v>
+        <v>2.946495536154888</v>
       </c>
       <c r="C188" t="n">
-        <v>0.7165284242788338</v>
+        <v>0.7755747753194212</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.01670670078287516</v>
+        <v>-0.01098113365584603</v>
       </c>
     </row>
     <row r="189">
@@ -3073,13 +3073,13 @@
         <v>1.87</v>
       </c>
       <c r="B189" t="n">
-        <v>3.037204490369415</v>
+        <v>2.934899633985022</v>
       </c>
       <c r="C189" t="n">
-        <v>0.7177345563885286</v>
+        <v>0.7769644539922005</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.01642970657356011</v>
+        <v>-0.01093473705208027</v>
       </c>
     </row>
     <row r="190">
@@ -3087,13 +3087,13 @@
         <v>1.88</v>
       </c>
       <c r="B190" t="n">
-        <v>3.026799860758796</v>
+        <v>2.923015544118847</v>
       </c>
       <c r="C190" t="n">
-        <v>0.7189759733254548</v>
+        <v>0.7783672048011644</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.01614074000380673</v>
+        <v>-0.01088479543933655</v>
       </c>
     </row>
     <row r="191">
@@ -3101,13 +3101,13 @@
         <v>1.89</v>
       </c>
       <c r="B191" t="n">
-        <v>3.016110420188408</v>
+        <v>2.910854468468004</v>
       </c>
       <c r="C191" t="n">
-        <v>0.7202519510038339</v>
+        <v>0.7797830157675421</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.01583969053379169</v>
+        <v>-0.0108311783158743</v>
       </c>
     </row>
     <row r="192">
@@ -3115,13 +3115,13 @@
         <v>1.9</v>
       </c>
       <c r="B192" t="n">
-        <v>3.005143352761264</v>
+        <v>2.898427565009322</v>
       </c>
       <c r="C192" t="n">
-        <v>0.7215617640174047</v>
+        <v>0.7812118750200501</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.01552644762369166</v>
+        <v>-0.01077375517995294</v>
       </c>
     </row>
     <row r="193">
@@ -3129,13 +3129,13 @@
         <v>1.91</v>
       </c>
       <c r="B193" t="n">
-        <v>2.99390586188445</v>
+        <v>2.885745938959982</v>
       </c>
       <c r="C193" t="n">
-        <v>0.7229046852515438</v>
+        <v>0.7826537707870324</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.0152009007336833</v>
+        <v>-0.01071239552983191</v>
       </c>
     </row>
     <row r="194">
@@ -3143,13 +3143,13 @@
         <v>1.92</v>
       </c>
       <c r="B194" t="n">
-        <v>2.982405165064002</v>
+        <v>2.872820634298102</v>
       </c>
       <c r="C194" t="n">
-        <v>0.7242799855034007</v>
+        <v>0.7841086913886055</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.01486293932394329</v>
+        <v>-0.01064696886377062</v>
       </c>
     </row>
     <row r="195">
@@ -3157,13 +3157,13 @@
         <v>1.93</v>
       </c>
       <c r="B195" t="n">
-        <v>2.97064848880533</v>
+        <v>2.859662625630617</v>
       </c>
       <c r="C195" t="n">
-        <v>0.7256869331099973</v>
+        <v>0.7855766252288053</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.01451245285464829</v>
+        <v>-0.01057734468002849</v>
       </c>
     </row>
     <row r="196">
@@ -3171,13 +3171,13 @@
         <v>1.94</v>
       </c>
       <c r="B196" t="n">
-        <v>2.958643063622172</v>
+        <v>2.846282810409579</v>
       </c>
       <c r="C196" t="n">
-        <v>0.7271247935842605</v>
+        <v>0.7870575607877363</v>
       </c>
       <c r="D196" t="n">
-        <v>-0.01414933078597497</v>
+        <v>-0.01050339247686495</v>
       </c>
     </row>
     <row r="197">
@@ -3185,13 +3185,13 @@
         <v>1.95</v>
       </c>
       <c r="B197" t="n">
-        <v>2.946396119156798</v>
+        <v>2.832692001497381</v>
       </c>
       <c r="C197" t="n">
-        <v>0.7285928292589579</v>
+        <v>0.7885514866137212</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.01377346257809999</v>
+        <v>-0.01042498175253942</v>
       </c>
     </row>
     <row r="198">
@@ -3199,13 +3199,13 @@
         <v>1.96</v>
       </c>
       <c r="B198" t="n">
-        <v>2.93391487941403</v>
+        <v>2.818900920080715</v>
       </c>
       <c r="C198" t="n">
-        <v>0.7300902989385283</v>
+        <v>0.7900583913154537</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.01338473769120003</v>
+        <v>-0.01034198200531133</v>
       </c>
     </row>
     <row r="199">
@@ -3213,13 +3213,13 @@
         <v>1.97</v>
       </c>
       <c r="B199" t="n">
-        <v>2.921206558111346</v>
+        <v>2.804920188932472</v>
       </c>
       <c r="C199" t="n">
-        <v>0.7316164575588041</v>
+        <v>0.791578263554148</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.01298304558545175</v>
+        <v>-0.0102542627334401</v>
       </c>
     </row>
     <row r="200">
@@ -3227,13 +3227,13 @@
         <v>1.98</v>
       </c>
       <c r="B200" t="n">
-        <v>2.908278354147177</v>
+        <v>2.790760326020182</v>
       </c>
       <c r="C200" t="n">
-        <v>0.733170555854636</v>
+        <v>0.793111092035689</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.01256827572103182</v>
+        <v>-0.01016169343518516</v>
       </c>
     </row>
     <row r="201">
@@ -3241,13 +3241,13 @@
         <v>1.99</v>
       </c>
       <c r="B201" t="n">
-        <v>2.895137447189269</v>
+        <v>2.776431738459047</v>
       </c>
       <c r="C201" t="n">
-        <v>0.7347518400354393</v>
+        <v>0.7946568655027815</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.01214031755811691</v>
+        <v>-0.01006414360880592</v>
       </c>
     </row>
     <row r="202">
@@ -3255,13 +3255,13 @@
         <v>2</v>
       </c>
       <c r="B202" t="n">
-        <v>2.881790993384755</v>
+        <v>2.761944716807059</v>
       </c>
       <c r="C202" t="n">
-        <v>0.7363595514686962</v>
+        <v>0.7962155727270963</v>
       </c>
       <c r="D202" t="n">
-        <v>-0.01169906055688369</v>
+        <v>-0.009961482752561809</v>
       </c>
     </row>
     <row r="203">
@@ -3269,13 +3269,13 @@
         <v>2.01</v>
       </c>
       <c r="B203" t="n">
-        <v>2.868246121193414</v>
+        <v>2.747309429699193</v>
       </c>
       <c r="C203" t="n">
-        <v>0.7379929263714532</v>
+        <v>0.7977872025014142</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.01124439417750881</v>
+        <v>-0.009853580364712252</v>
       </c>
     </row>
     <row r="204">
@@ -3283,13 +3283,13 @@
         <v>2.02</v>
       </c>
       <c r="B204" t="n">
-        <v>2.854509927345363</v>
+        <v>2.73253591881719</v>
       </c>
       <c r="C204" t="n">
-        <v>0.7396511955098655</v>
+        <v>0.7993717436317654</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.01077620788016897</v>
+        <v>-0.009740305943516677</v>
       </c>
     </row>
     <row r="205">
@@ -3297,13 +3297,13 @@
         <v>2.03</v>
       </c>
       <c r="B205" t="n">
-        <v>2.840589472924234</v>
+        <v>2.717634094190991</v>
       </c>
       <c r="C205" t="n">
-        <v>0.7413335839068533</v>
+        <v>0.800969184929567</v>
       </c>
       <c r="D205" t="n">
-        <v>-0.0102943911250408</v>
+        <v>-0.009621528987234501</v>
       </c>
     </row>
     <row r="206">
@@ -3311,13 +3311,13 @@
         <v>2.04</v>
       </c>
       <c r="B206" t="n">
-        <v>2.826491779576711</v>
+        <v>2.702613729827437</v>
       </c>
       <c r="C206" t="n">
-        <v>0.7430393105579366</v>
+        <v>0.8025795152037531</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.009798833372301009</v>
+        <v>-0.009497118994125156</v>
       </c>
     </row>
     <row r="207">
@@ -3325,13 +3325,13 @@
         <v>2.05</v>
       </c>
       <c r="B207" t="n">
-        <v>2.812223825849087</v>
+        <v>2.687484459661492</v>
       </c>
       <c r="C207" t="n">
-        <v>0.7447675881553335</v>
+        <v>0.8042027232529025</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.009289424082126248</v>
+        <v>-0.009366945462448059</v>
       </c>
     </row>
     <row r="208">
@@ -3339,13 +3339,13 @@
         <v>2.06</v>
       </c>
       <c r="B208" t="n">
-        <v>2.797792543651355</v>
+        <v>2.67225577382485</v>
       </c>
       <c r="C208" t="n">
-        <v>0.7465176228204095</v>
+        <v>0.8058387978573583</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.008766052714693159</v>
+        <v>-0.009230877890462629</v>
       </c>
     </row>
     <row r="209">
@@ -3353,13 +3353,13 @@
         <v>2.07</v>
       </c>
       <c r="B209" t="n">
-        <v>2.783204814849134</v>
+        <v>2.65693701522645</v>
       </c>
       <c r="C209" t="n">
-        <v>0.7482886138445771</v>
+        <v>0.8074877277713427</v>
       </c>
       <c r="D209" t="n">
-        <v>-0.008228608730178453</v>
+        <v>-0.009088785776428302</v>
       </c>
     </row>
     <row r="210">
@@ -3367,13 +3367,13 @@
         <v>2.08</v>
       </c>
       <c r="B210" t="n">
-        <v>2.768467467983569</v>
+        <v>2.641537376439107</v>
       </c>
       <c r="C210" t="n">
-        <v>0.750079753438754</v>
+        <v>0.8091495017150635</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.007676981588758753</v>
+        <v>-0.008940538618604488</v>
       </c>
     </row>
     <row r="211">
@@ -3381,13 +3381,13 @@
         <v>2.09</v>
       </c>
       <c r="B211" t="n">
-        <v>2.753587275119198</v>
+        <v>2.626065896886217</v>
       </c>
       <c r="C211" t="n">
-        <v>0.7518902264914938</v>
+        <v>0.8108241083668147</v>
       </c>
       <c r="D211" t="n">
-        <v>-0.007111060750610774</v>
+        <v>-0.008786005915250625</v>
       </c>
     </row>
     <row r="212">
@@ -3395,13 +3395,13 @@
         <v>2.1</v>
       </c>
       <c r="B212" t="n">
-        <v>2.738570948819583</v>
+        <v>2.610531460322156</v>
       </c>
       <c r="C212" t="n">
-        <v>0.7537192103359157</v>
+        <v>0.812511536355068</v>
       </c>
       <c r="D212" t="n">
-        <v>-0.006530735675911139</v>
+        <v>-0.008625057164626124</v>
       </c>
     </row>
     <row r="213">
@@ -3409,13 +3409,13 @@
         <v>2.11</v>
       </c>
       <c r="B213" t="n">
-        <v>2.723425139250377</v>
+        <v>2.59494279259985</v>
       </c>
       <c r="C213" t="n">
-        <v>0.7555658745255618</v>
+        <v>0.8142117742505558</v>
       </c>
       <c r="D213" t="n">
-        <v>-0.005935895824836562</v>
+        <v>-0.00845756186499042</v>
       </c>
     </row>
     <row r="214">
@@ -3423,13 +3423,13 @@
         <v>2.12</v>
       </c>
       <c r="B214" t="n">
-        <v>2.708156431409323</v>
+        <v>2.5793084597187</v>
       </c>
       <c r="C214" t="n">
-        <v>0.7574293806193241</v>
+        <v>0.8159248105583464</v>
       </c>
       <c r="D214" t="n">
-        <v>-0.005326430657563656</v>
+        <v>-0.008283389514602921</v>
       </c>
     </row>
     <row r="215">
@@ -3437,13 +3437,13 @@
         <v>2.13</v>
       </c>
       <c r="B215" t="n">
-        <v>2.692771342482561</v>
+        <v>2.563636866145931</v>
       </c>
       <c r="C215" t="n">
-        <v>0.7593088819755864</v>
+        <v>0.8176506337099082</v>
       </c>
       <c r="D215" t="n">
-        <v>-0.00470222963426915</v>
+        <v>-0.008102409611723069</v>
       </c>
     </row>
     <row r="216">
@@ -3451,13 +3451,13 @@
         <v>2.14</v>
       </c>
       <c r="B216" t="n">
-        <v>2.677276319326454</v>
+        <v>2.547936253404211</v>
       </c>
       <c r="C216" t="n">
-        <v>0.7612035235557353</v>
+        <v>0.8193892320551655</v>
       </c>
       <c r="D216" t="n">
-        <v>-0.004063182215129656</v>
+        <v>-0.007914491654610271</v>
       </c>
     </row>
     <row r="217">
@@ -3465,13 +3465,13 @@
         <v>2.15</v>
       </c>
       <c r="B217" t="n">
-        <v>2.661677736074044</v>
+        <v>2.532214698918302</v>
       </c>
       <c r="C217" t="n">
-        <v>0.7631124417371989</v>
+        <v>0.8211405938545422</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.00340917786032189</v>
+        <v>-0.007719505141523968</v>
       </c>
     </row>
     <row r="218">
@@ -3479,13 +3479,13 @@
         <v>2.16</v>
       </c>
       <c r="B218" t="n">
-        <v>2.645981891865079</v>
+        <v>2.516480115113331</v>
       </c>
       <c r="C218" t="n">
-        <v>0.7650347641361841</v>
+        <v>0.8229047072709968</v>
       </c>
       <c r="D218" t="n">
-        <v>-0.002740106030022473</v>
+        <v>-0.007517319570723564</v>
       </c>
     </row>
     <row r="219">
@@ -3493,13 +3493,13 @@
         <v>2.17</v>
       </c>
       <c r="B219" t="n">
-        <v>2.630195008698482</v>
+        <v>2.500740248757246</v>
       </c>
       <c r="C219" t="n">
-        <v>0.7669696094402795</v>
+        <v>0.8246815603620449</v>
       </c>
       <c r="D219" t="n">
-        <v>-0.002055856184408125</v>
+        <v>-0.007307804440468503</v>
       </c>
     </row>
     <row r="220">
@@ -3507,13 +3507,13 @@
         <v>2.18</v>
       </c>
       <c r="B220" t="n">
-        <v>2.614323229405961</v>
+        <v>2.485002680539863</v>
       </c>
       <c r="C220" t="n">
-        <v>0.768916087251109</v>
+        <v>0.8264711410717696</v>
       </c>
       <c r="D220" t="n">
-        <v>-0.001356317783655454</v>
+        <v>-0.00709082924901819</v>
       </c>
     </row>
     <row r="221">
@@ -3521,13 +3521,13 @@
         <v>2.19</v>
       </c>
       <c r="B221" t="n">
-        <v>2.598372615745411</v>
+        <v>2.469274824880937</v>
       </c>
       <c r="C221" t="n">
-        <v>0.7708732979372148</v>
+        <v>0.8282734372228211</v>
       </c>
       <c r="D221" t="n">
-        <v>-0.0006413802879411917</v>
+        <v>-0.006866263494632065</v>
       </c>
     </row>
     <row r="222">
@@ -3535,13 +3535,13 @@
         <v>2.2</v>
       </c>
       <c r="B222" t="n">
-        <v>2.582349146612595</v>
+        <v>2.4535639299596</v>
       </c>
       <c r="C222" t="n">
-        <v>0.7728403324973639</v>
+        <v>0.8300884365084038</v>
       </c>
       <c r="D222" t="n">
-        <v>8.906684255805767e-05</v>
+        <v>-0.006633976675569533</v>
       </c>
     </row>
     <row r="223">
@@ -3549,13 +3549,13 @@
         <v>2.21</v>
       </c>
       <c r="B223" t="n">
-        <v>2.566258716369537</v>
+        <v>2.437877077957515</v>
       </c>
       <c r="C223" t="n">
-        <v>0.7748162724344678</v>
+        <v>0.8319161264842498</v>
       </c>
       <c r="D223" t="n">
-        <v>0.0008351341476655616</v>
+        <v>-0.006393838290090041</v>
       </c>
     </row>
     <row r="224">
@@ -3563,13 +3563,13 @@
         <v>2.22</v>
       </c>
       <c r="B224" t="n">
-        <v>2.550107133287951</v>
+        <v>2.422221185508092</v>
       </c>
       <c r="C224" t="n">
-        <v>0.7768001896403189</v>
+        <v>0.83375649456058</v>
       </c>
       <c r="D224" t="n">
-        <v>0.001596932167204718</v>
+        <v>-0.006145717836452989</v>
       </c>
     </row>
     <row r="225">
@@ -3577,13 +3577,13 @@
         <v>2.23</v>
       </c>
       <c r="B225" t="n">
-        <v>2.533900118105935</v>
+        <v>2.406603004344142</v>
       </c>
       <c r="C225" t="n">
-        <v>0.7787911462913427</v>
+        <v>0.8356095279940512</v>
       </c>
       <c r="D225" t="n">
-        <v>0.002374571440998791</v>
+        <v>-0.005889484812917821</v>
       </c>
     </row>
     <row r="226">
@@ -3591,13 +3591,13 @@
         <v>2.24</v>
       </c>
       <c r="B226" t="n">
-        <v>2.517643302696102</v>
+        <v>2.391029122136351</v>
       </c>
       <c r="C226" t="n">
-        <v>0.7807881947555748</v>
+        <v>0.8374752138796902</v>
       </c>
       <c r="D226" t="n">
-        <v>0.003168162508871186</v>
+        <v>-0.005625008717743941</v>
       </c>
     </row>
     <row r="227">
@@ -3605,13 +3605,13 @@
         <v>2.25</v>
       </c>
       <c r="B227" t="n">
-        <v>2.501342228843216</v>
+        <v>2.375505963515037</v>
       </c>
       <c r="C227" t="n">
-        <v>0.7827903775110714</v>
+        <v>0.8393535391428131</v>
       </c>
       <c r="D227" t="n">
-        <v>0.003977815910645155</v>
+        <v>-0.005352159049190796</v>
       </c>
     </row>
     <row r="228">
@@ -3619,13 +3619,13 @@
         <v>2.26</v>
       </c>
       <c r="B228" t="n">
-        <v>2.485002347129353</v>
+        <v>2.360039791267699</v>
       </c>
       <c r="C228" t="n">
-        <v>0.7847967270759687</v>
+        <v>0.8412444905309313</v>
       </c>
       <c r="D228" t="n">
-        <v>0.004803642186144113</v>
+        <v>-0.005070805305517782</v>
       </c>
     </row>
     <row r="229">
@@ -3633,13 +3633,13 @@
         <v>2.27</v>
       </c>
       <c r="B229" t="n">
-        <v>2.468629015924536</v>
+        <v>2.34463670770495</v>
       </c>
       <c r="C229" t="n">
-        <v>0.7868062659504031</v>
+        <v>0.8431480546056409</v>
       </c>
       <c r="D229" t="n">
-        <v>0.005645751875191312</v>
+        <v>-0.004780816984984353</v>
       </c>
     </row>
     <row r="230">
@@ -3647,13 +3647,13 @@
         <v>2.28</v>
       </c>
       <c r="B230" t="n">
-        <v>2.452227500480715</v>
+        <v>2.329302656187515</v>
       </c>
       <c r="C230" t="n">
-        <v>0.7888180065705157</v>
+        <v>0.8450642177344998</v>
       </c>
       <c r="D230" t="n">
-        <v>0.006504255517610162</v>
+        <v>-0.004482063585849902</v>
       </c>
     </row>
     <row r="231">
@@ -3661,13 +3661,13 @@
         <v>2.29</v>
       </c>
       <c r="B231" t="n">
-        <v>2.435802972126956</v>
+        <v>2.314043422807085</v>
       </c>
       <c r="C231" t="n">
-        <v>0.7908309512747547</v>
+        <v>0.8469929660828871</v>
       </c>
       <c r="D231" t="n">
-        <v>0.007379263653223917</v>
+        <v>-0.004174414606373879</v>
       </c>
     </row>
     <row r="232">
@@ -3675,13 +3675,13 @@
         <v>2.3</v>
       </c>
       <c r="B232" t="n">
-        <v>2.419360507563593</v>
+        <v>2.298864638213906</v>
       </c>
       <c r="C232" t="n">
-        <v>0.792844092282703</v>
+        <v>0.8489342856058495</v>
       </c>
       <c r="D232" t="n">
-        <v>0.008270886821855988</v>
+        <v>-0.003857739544815687</v>
       </c>
     </row>
     <row r="233">
@@ -3689,13 +3689,13 @@
         <v>2.31</v>
       </c>
       <c r="B233" t="n">
-        <v>2.402905088253104</v>
+        <v>2.283771779584166</v>
       </c>
       <c r="C233" t="n">
-        <v>0.7948564116866486</v>
+        <v>0.8508881620399299</v>
       </c>
       <c r="D233" t="n">
-        <v>0.009179235563329625</v>
+        <v>-0.00353190789943477</v>
       </c>
     </row>
     <row r="234">
@@ -3703,13 +3703,13 @@
         <v>2.32</v>
       </c>
       <c r="B234" t="n">
-        <v>2.386441599905392</v>
+        <v>2.26877017272029</v>
       </c>
       <c r="C234" t="n">
-        <v>0.7968668814561235</v>
+        <v>0.8528545808949817</v>
       </c>
       <c r="D234" t="n">
-        <v>0.0101044204174682</v>
+        <v>-0.003196789168490541</v>
       </c>
     </row>
     <row r="235">
@@ -3717,13 +3717,13 @@
         <v>2.33</v>
       </c>
       <c r="B235" t="n">
-        <v>2.369974832055165</v>
+        <v>2.253864994277489</v>
       </c>
       <c r="C235" t="n">
-        <v>0.7988744634556324</v>
+        <v>0.8548335274459665</v>
       </c>
       <c r="D235" t="n">
-        <v>0.01104655192409509</v>
+        <v>-0.002852252850242411</v>
       </c>
     </row>
     <row r="236">
@@ -3731,13 +3731,13 @@
         <v>2.34</v>
       </c>
       <c r="B236" t="n">
-        <v>2.353509477729022</v>
+        <v>2.23906127410999</v>
       </c>
       <c r="C236" t="n">
-        <v>0.8008781094757933</v>
+        <v>0.8568249867247361</v>
       </c>
       <c r="D236" t="n">
-        <v>0.01200574062303355</v>
+        <v>-0.002498168442949826</v>
       </c>
     </row>
     <row r="237">
@@ -3745,13 +3745,13 @@
         <v>2.35</v>
       </c>
       <c r="B237" t="n">
-        <v>2.33705013319987</v>
+        <v>2.224363897730579</v>
       </c>
       <c r="C237" t="n">
-        <v>0.8028767612781136</v>
+        <v>0.8588289435117971</v>
       </c>
       <c r="D237" t="n">
-        <v>0.01298209705410698</v>
+        <v>-0.002134405444872188</v>
       </c>
     </row>
     <row r="238">
@@ -3759,13 +3759,13 @@
         <v>2.36</v>
       </c>
       <c r="B238" t="n">
-        <v>2.320601297826267</v>
+        <v>2.209777608877233</v>
       </c>
       <c r="C238" t="n">
-        <v>0.8048693506536184</v>
+        <v>0.8608453823280603</v>
       </c>
       <c r="D238" t="n">
-        <v>0.01397573175713864</v>
+        <v>-0.001760833354268946</v>
       </c>
     </row>
     <row r="239">
@@ -3773,13 +3773,13 @@
         <v>2.37</v>
       </c>
       <c r="B239" t="n">
-        <v>2.304167373974241</v>
+        <v>2.195307012180796</v>
       </c>
       <c r="C239" t="n">
-        <v>0.8068547994955534</v>
+        <v>0.8628742874265727</v>
       </c>
       <c r="D239" t="n">
-        <v>0.01498675527195194</v>
+        <v>-0.001377321669399495</v>
       </c>
     </row>
     <row r="240">
@@ -3787,13 +3787,13 @@
         <v>2.38</v>
       </c>
       <c r="B240" t="n">
-        <v>2.287752667019173</v>
+        <v>2.180956575927855</v>
       </c>
       <c r="C240" t="n">
-        <v>0.8088320198863734</v>
+        <v>0.8649156427842331</v>
       </c>
       <c r="D240" t="n">
-        <v>0.01601527813837013</v>
+        <v>-0.0009837398885232888</v>
       </c>
     </row>
     <row r="241">
@@ -3801,13 +3801,13 @@
         <v>2.39</v>
       </c>
       <c r="B241" t="n">
-        <v>2.271361385425263</v>
+        <v>2.16673063491311</v>
       </c>
       <c r="C241" t="n">
-        <v>0.8107999141992337</v>
+        <v>0.8669694320934905</v>
       </c>
       <c r="D241" t="n">
-        <v>0.01706141089621664</v>
+        <v>-0.0005799575098997169</v>
       </c>
     </row>
     <row r="242">
@@ -3815,13 +3815,13 @@
         <v>2.4</v>
       </c>
       <c r="B242" t="n">
-        <v>2.254997640900155</v>
+        <v>2.152633393375789</v>
       </c>
       <c r="C242" t="n">
-        <v>0.8127573752141902</v>
+        <v>0.869035638754026</v>
       </c>
       <c r="D242" t="n">
-        <v>0.01812526408531468</v>
+        <v>-0.000165844031788244</v>
       </c>
     </row>
     <row r="243">
@@ -3829,13 +3829,13 @@
         <v>2.41</v>
       </c>
       <c r="B243" t="n">
-        <v>2.238665448622232</v>
+        <v>2.138668928014783</v>
       </c>
       <c r="C243" t="n">
-        <v>0.8147032862493166</v>
+        <v>0.8711142458644178</v>
       </c>
       <c r="D243" t="n">
-        <v>0.01920694824548772</v>
+        <v>0.0002587310475517506</v>
       </c>
     </row>
     <row r="244">
@@ -3843,13 +3843,13 @@
         <v>2.42</v>
       </c>
       <c r="B244" t="n">
-        <v>2.222368727538158</v>
+        <v>2.124841191077438</v>
       </c>
       <c r="C244" t="n">
-        <v>0.8166365213069364</v>
+        <v>0.8732052362137882</v>
       </c>
       <c r="D244" t="n">
-        <v>0.02030657391655896</v>
+        <v>0.0006938982298608024</v>
       </c>
     </row>
     <row r="245">
@@ -3857,13 +3857,13 @@
         <v>2.43</v>
       </c>
       <c r="B245" t="n">
-        <v>2.206111300728183</v>
+        <v>2.111154013517098</v>
       </c>
       <c r="C245" t="n">
-        <v>0.8185559452351684</v>
+        <v>0.8753085922734352</v>
       </c>
       <c r="D245" t="n">
-        <v>0.02142425163835183</v>
+        <v>0.001139788016879523</v>
       </c>
     </row>
     <row r="246">
@@ -3871,13 +3871,13 @@
         <v>2.44</v>
       </c>
       <c r="B246" t="n">
-        <v>2.189896895836802</v>
+        <v>2.097611108214727</v>
       </c>
       <c r="C246" t="n">
-        <v>0.8204604139049722</v>
+        <v>0.8774242961884449</v>
       </c>
       <c r="D246" t="n">
-        <v>0.02256009195068959</v>
+        <v>0.001596530910348455</v>
       </c>
     </row>
     <row r="247">
@@ -3885,13 +3885,13 @@
         <v>2.45</v>
       </c>
       <c r="B247" t="n">
-        <v>2.173729145566313</v>
+        <v>2.084216073260126</v>
       </c>
       <c r="C247" t="n">
-        <v>0.8223487744028818</v>
+        <v>0.8795523297692889</v>
       </c>
       <c r="D247" t="n">
-        <v>0.02371420539339567</v>
+        <v>0.00206425741200821</v>
       </c>
     </row>
     <row r="248">
@@ -3899,13 +3899,13 @@
         <v>2.46</v>
       </c>
       <c r="B248" t="n">
-        <v>2.157611588230881</v>
+        <v>2.070972395288485</v>
       </c>
       <c r="C248" t="n">
-        <v>0.8242198652395986</v>
+        <v>0.8816926744834028</v>
       </c>
       <c r="D248" t="n">
-        <v>0.02488670250629327</v>
+        <v>0.002543098023599328</v>
       </c>
     </row>
     <row r="249">
@@ -3913,13 +3913,13 @@
         <v>2.47</v>
       </c>
       <c r="B249" t="n">
-        <v>2.141547668368674</v>
+        <v>2.057883452868221</v>
       </c>
       <c r="C249" t="n">
-        <v>0.8260725165746178</v>
+        <v>0.8838453114467493</v>
       </c>
       <c r="D249" t="n">
-        <v>0.02607769382920585</v>
+        <v>0.003033183246862426</v>
       </c>
     </row>
     <row r="250">
@@ -3927,13 +3927,13 @@
         <v>2.48</v>
       </c>
       <c r="B250" t="n">
-        <v>2.125540737409746</v>
+        <v>2.044952519936254</v>
       </c>
       <c r="C250" t="n">
-        <v>0.8279055504570464</v>
+        <v>0.8860102214153622</v>
       </c>
       <c r="D250" t="n">
-        <v>0.02728728990195663</v>
+        <v>0.003534643583538033</v>
       </c>
     </row>
     <row r="251">
@@ -3941,13 +3941,13 @@
         <v>2.49</v>
       </c>
       <c r="B251" t="n">
-        <v>2.109594054397258</v>
+        <v>2.032182769277106</v>
       </c>
       <c r="C251" t="n">
-        <v>0.8297177810827663</v>
+        <v>0.8881873847768756</v>
       </c>
       <c r="D251" t="n">
-        <v>0.02851560126436905</v>
+        <v>0.004047609535366776</v>
       </c>
     </row>
     <row r="252">
@@ -3955,13 +3955,13 @@
         <v>2.5</v>
       </c>
       <c r="B252" t="n">
-        <v>2.093710786759744</v>
+        <v>2.0195772760424</v>
       </c>
       <c r="C252" t="n">
-        <v>0.8315080150680852</v>
+        <v>0.8903767815420344</v>
       </c>
       <c r="D252" t="n">
-        <v>0.02976273845626633</v>
+        <v>0.004572211604089183</v>
       </c>
     </row>
     <row r="253">
@@ -3969,13 +3969,13 @@
         <v>2.51</v>
       </c>
       <c r="B253" t="n">
-        <v>2.077894011132096</v>
+        <v>2.007139021307589</v>
       </c>
       <c r="C253" t="n">
-        <v>0.8332750517400094</v>
+        <v>0.8925783913361892</v>
       </c>
       <c r="D253" t="n">
-        <v>0.03102881201747191</v>
+        <v>0.005108580291445872</v>
       </c>
     </row>
     <row r="254">
@@ -3983,13 +3983,13 @@
         <v>2.52</v>
       </c>
       <c r="B254" t="n">
-        <v>2.062146714223011</v>
+        <v>1.994870895662916</v>
       </c>
       <c r="C254" t="n">
-        <v>0.8350176834432577</v>
+        <v>0.8947921933907735</v>
       </c>
       <c r="D254" t="n">
-        <v>0.03231393248780902</v>
+        <v>0.005656846099177383</v>
       </c>
     </row>
     <row r="255">
@@ -3997,13 +3997,13 @@
         <v>2.53</v>
       </c>
       <c r="B255" t="n">
-        <v>2.046471793726638</v>
+        <v>1.982775702835856</v>
       </c>
       <c r="C255" t="n">
-        <v>0.8367346958641331</v>
+        <v>0.8970181665347656</v>
       </c>
       <c r="D255" t="n">
-        <v>0.03361821040710111</v>
+        <v>0.006217139529024331</v>
       </c>
     </row>
     <row r="256">
@@ -4011,13 +4011,13 @@
         <v>2.54</v>
       </c>
       <c r="B256" t="n">
-        <v>2.030872059276244</v>
+        <v>1.970856163342499</v>
       </c>
       <c r="C256" t="n">
-        <v>0.838424868371346</v>
+        <v>0.8992562891861319</v>
       </c>
       <c r="D256" t="n">
-        <v>0.03494175631517139</v>
+        <v>0.006789591082727248</v>
       </c>
     </row>
     <row r="257">
@@ -4025,13 +4025,13 @@
         <v>2.55</v>
       </c>
       <c r="B257" t="n">
-        <v>2.015350233437685</v>
+        <v>1.959114918165546</v>
       </c>
       <c r="C257" t="n">
-        <v>0.8400869743738798</v>
+        <v>0.9015065393432561</v>
       </c>
       <c r="D257" t="n">
-        <v>0.0362846807518433</v>
+        <v>0.007374331262026756</v>
       </c>
     </row>
     <row r="258">
@@ -4039,13 +4039,13 @@
         <v>2.56</v>
       </c>
       <c r="B258" t="n">
-        <v>1.999908952740587</v>
+        <v>1.947554532456808</v>
       </c>
       <c r="C258" t="n">
-        <v>0.8417197816959696</v>
+        <v>0.9037688945763508</v>
       </c>
       <c r="D258" t="n">
-        <v>0.03764709425694005</v>
+        <v>0.007971490568663388</v>
       </c>
     </row>
     <row r="259">
@@ -4053,13 +4053,13 @@
         <v>2.57</v>
       </c>
       <c r="B259" t="n">
-        <v>1.984550768745102</v>
+        <v>1.936177499262312</v>
       </c>
       <c r="C259" t="n">
-        <v>0.8433220529692563</v>
+        <v>0.9060433320188539</v>
       </c>
       <c r="D259" t="n">
-        <v>0.03902910737028505</v>
+        <v>0.008581199504377737</v>
       </c>
     </row>
     <row r="260">
@@ -4067,13 +4067,13 @@
         <v>2.58</v>
       </c>
       <c r="B260" t="n">
-        <v>1.969278149142201</v>
+        <v>1.924986243268345</v>
       </c>
       <c r="C260" t="n">
-        <v>0.8448925460421598</v>
+        <v>0.9083298283588093</v>
       </c>
       <c r="D260" t="n">
-        <v>0.04043083063170169</v>
+        <v>0.00920358857091041</v>
       </c>
     </row>
     <row r="261">
@@ -4081,13 +4081,13 @@
         <v>2.59</v>
       </c>
       <c r="B261" t="n">
-        <v>1.95409347888548</v>
+        <v>1.913983124566967</v>
       </c>
       <c r="C261" t="n">
-        <v>0.8464300144065016</v>
+        <v>0.9106283598302302</v>
       </c>
       <c r="D261" t="n">
-        <v>0.04185237458101317</v>
+        <v>0.009838788270001932</v>
       </c>
     </row>
     <row r="262">
@@ -4095,13 +4095,13 @@
         <v>2.6</v>
       </c>
       <c r="B262" t="n">
-        <v>1.938999061352485</v>
+        <v>1.903170442439736</v>
       </c>
       <c r="C262" t="n">
-        <v>0.8479332076413926</v>
+        <v>0.9129389022044503</v>
       </c>
       <c r="D262" t="n">
-        <v>0.04329384975804296</v>
+        <v>0.01048692910339293</v>
       </c>
     </row>
     <row r="263">
@@ -4109,13 +4109,13 @@
         <v>2.61</v>
       </c>
       <c r="B263" t="n">
-        <v>1.923997119533656</v>
+        <v>1.892550439158642</v>
       </c>
       <c r="C263" t="n">
-        <v>0.8494008718743827</v>
+        <v>0.9152614307814568</v>
       </c>
       <c r="D263" t="n">
-        <v>0.04475536670261424</v>
+        <v>0.01114814157282393</v>
       </c>
     </row>
     <row r="264">
@@ -4123,13 +4123,13 @@
         <v>2.62</v>
       </c>
       <c r="B264" t="n">
-        <v>1.909089797246959</v>
+        <v>1.882125303803385</v>
       </c>
       <c r="C264" t="n">
-        <v>0.8508317502598545</v>
+        <v>0.9175959203812114</v>
       </c>
       <c r="D264" t="n">
-        <v>0.0462370359545505</v>
+        <v>0.01182255618003555</v>
       </c>
     </row>
     <row r="265">
@@ -4137,13 +4137,13 @@
         <v>2.63</v>
       </c>
       <c r="B265" t="n">
-        <v>1.894279160376395</v>
+        <v>1.871897176094431</v>
       </c>
       <c r="C265" t="n">
-        <v>0.8522245834746223</v>
+        <v>0.9199423453349538</v>
       </c>
       <c r="D265" t="n">
-        <v>0.04773896805367492</v>
+        <v>0.01251030342676834</v>
       </c>
     </row>
     <row r="266">
@@ -4151,13 +4151,13 @@
         <v>2.64</v>
       </c>
       <c r="B266" t="n">
-        <v>1.879567198132562</v>
+        <v>1.861868150241423</v>
       </c>
       <c r="C266" t="n">
-        <v>0.8535781102306854</v>
+        <v>0.9223006794764936</v>
       </c>
       <c r="D266" t="n">
-        <v>0.049261273539811</v>
+        <v>0.0132115138147629</v>
       </c>
     </row>
     <row r="267">
@@ -4165,13 +4165,13 @@
         <v>2.65</v>
       </c>
       <c r="B267" t="n">
-        <v>1.864955824333537</v>
+        <v>1.852040278806787</v>
       </c>
       <c r="C267" t="n">
-        <v>0.8548910678050584</v>
+        <v>0.9246708961334871</v>
       </c>
       <c r="D267" t="n">
-        <v>0.05080406295278188</v>
+        <v>0.01392631784575977</v>
       </c>
     </row>
     <row r="268">
@@ -4179,13 +4179,13 @@
         <v>2.66</v>
       </c>
       <c r="B268" t="n">
-        <v>1.850446878704342</v>
+        <v>1.842415576584537</v>
       </c>
       <c r="C268" t="n">
-        <v>0.8561621925865859</v>
+        <v>0.9270529681187006</v>
       </c>
       <c r="D268" t="n">
-        <v>0.05236744683241108</v>
+        <v>0.01465484602149958</v>
       </c>
     </row>
     <row r="269">
@@ -4193,13 +4193,13 @@
         <v>2.67</v>
       </c>
       <c r="B269" t="n">
-        <v>1.836042128193372</v>
+        <v>1.83299602449455</v>
       </c>
       <c r="C269" t="n">
-        <v>0.8573902206396306</v>
+        <v>0.9294468677212605</v>
       </c>
       <c r="D269" t="n">
-        <v>0.05395153571852175</v>
+        <v>0.01539722884372284</v>
       </c>
     </row>
     <row r="270">
@@ -4207,13 +4207,13 @@
         <v>2.68</v>
       </c>
       <c r="B270" t="n">
-        <v>1.821743268304137</v>
+        <v>1.82378357349274</v>
       </c>
       <c r="C270" t="n">
-        <v>0.8585738882844977</v>
+        <v>0.9318525666978913</v>
       </c>
       <c r="D270" t="n">
-        <v>0.0555564401509374</v>
+        <v>0.01615359681417019</v>
       </c>
     </row>
     <row r="271">
@@ -4221,13 +4221,13 @@
         <v>2.69</v>
       </c>
       <c r="B271" t="n">
-        <v>1.80755192444078</v>
+        <v>1.814780148497818</v>
       </c>
       <c r="C271" t="n">
-        <v>0.8597119326944428</v>
+        <v>0.9342700362641398</v>
       </c>
       <c r="D271" t="n">
-        <v>0.05718227066948121</v>
+        <v>0.01692408043458215</v>
       </c>
     </row>
     <row r="272">
@@ -4235,13 +4235,13 @@
         <v>2.7</v>
       </c>
       <c r="B272" t="n">
-        <v>1.793469653265835</v>
+        <v>1.805987652335499</v>
       </c>
       <c r="C272" t="n">
-        <v>0.8608030925090843</v>
+        <v>0.9366992470855888</v>
       </c>
       <c r="D272" t="n">
-        <v>0.05882913781397665</v>
+        <v>0.01770881020669936</v>
       </c>
     </row>
     <row r="273">
@@ -4249,13 +4249,13 @@
         <v>2.71</v>
       </c>
       <c r="B273" t="n">
-        <v>1.779497944068776</v>
+        <v>1.797407969701269</v>
       </c>
       <c r="C273" t="n">
-        <v>0.8618461084640231</v>
+        <v>0.9391401692690582</v>
       </c>
       <c r="D273" t="n">
-        <v>0.0604971521242469</v>
+        <v>0.01850791663226232</v>
       </c>
     </row>
     <row r="274">
@@ -4263,13 +4263,13 @@
         <v>2.72</v>
       </c>
       <c r="B274" t="n">
-        <v>1.765638220143923</v>
+        <v>1.789042971142999</v>
       </c>
       <c r="C274" t="n">
-        <v>0.8628397240364455</v>
+        <v>0.9415927723537951</v>
       </c>
       <c r="D274" t="n">
-        <v>0.06218642414011546</v>
+        <v>0.01932153021301168</v>
       </c>
     </row>
     <row r="275">
@@ -4277,13 +4277,13 @@
         <v>2.73</v>
       </c>
       <c r="B275" t="n">
-        <v>1.75189184017634</v>
+        <v>1.780894517064955</v>
       </c>
       <c r="C275" t="n">
-        <v>0.8637826861064654</v>
+        <v>0.9440570253026537</v>
       </c>
       <c r="D275" t="n">
-        <v>0.0638970644014055</v>
+        <v>0.02014978145068795</v>
       </c>
     </row>
     <row r="276">
@@ -4291,13 +4291,13 @@
         <v>2.74</v>
       </c>
       <c r="B276" t="n">
-        <v>1.7382600996344</v>
+        <v>1.772964461754915</v>
       </c>
       <c r="C276" t="n">
-        <v>0.8646737456339347</v>
+        <v>0.9465328964932648</v>
       </c>
       <c r="D276" t="n">
-        <v>0.0656291834479405</v>
+        <v>0.02099280084703178</v>
       </c>
     </row>
     <row r="277">
@@ -4305,13 +4305,13 @@
         <v>2.75</v>
       </c>
       <c r="B277" t="n">
-        <v>1.724744232167748</v>
+        <v>1.765254657436381</v>
       </c>
       <c r="C277" t="n">
-        <v>0.8655116583504315</v>
+        <v>0.9490203537091949</v>
       </c>
       <c r="D277" t="n">
-        <v>0.06738289181954364</v>
+        <v>0.02185071890378366</v>
       </c>
     </row>
     <row r="278">
@@ -4319,13 +4319,13 @@
         <v>2.76</v>
       </c>
       <c r="B278" t="n">
-        <v>1.711345411009429</v>
+        <v>1.757766958348058</v>
       </c>
       <c r="C278" t="n">
-        <v>0.866295185466104</v>
+        <v>0.9515193641310976</v>
       </c>
       <c r="D278" t="n">
-        <v>0.06915830005603842</v>
+        <v>0.02272366612268426</v>
       </c>
     </row>
     <row r="279">
@@ -4333,13 +4333,13 @@
         <v>2.77</v>
       </c>
       <c r="B279" t="n">
-        <v>1.698064750381006</v>
+        <v>1.750503224852995</v>
       </c>
       <c r="C279" t="n">
-        <v>0.8670230943910293</v>
+        <v>0.9540298943278547</v>
       </c>
       <c r="D279" t="n">
-        <v>0.07095551869724798</v>
+        <v>0.02361177300547407</v>
       </c>
     </row>
     <row r="280">
@@ -4347,13 +4347,13 @@
         <v>2.78</v>
       </c>
       <c r="B280" t="n">
-        <v>1.684903306899531</v>
+        <v>1.743465327580044</v>
       </c>
       <c r="C280" t="n">
-        <v>0.8676941594707199</v>
+        <v>0.9565519102477107</v>
       </c>
       <c r="D280" t="n">
-        <v>0.07277465828299585</v>
+        <v>0.02451517005389373</v>
       </c>
     </row>
     <row r="281">
@@ -4361,13 +4361,13 @@
         <v>2.79</v>
       </c>
       <c r="B281" t="n">
-        <v>1.671862080985301</v>
+        <v>1.736655151600483</v>
       </c>
       <c r="C281" t="n">
-        <v>0.8683071627353781</v>
+        <v>0.9590853772093987</v>
       </c>
       <c r="D281" t="n">
-        <v>0.07461582935310521</v>
+        <v>0.02543398776968377</v>
       </c>
     </row>
     <row r="282">
@@ -4375,13 +4375,13 @@
         <v>2.8</v>
       </c>
       <c r="B282" t="n">
-        <v>1.658942018269334</v>
+        <v>1.730074600642907</v>
       </c>
       <c r="C282" t="n">
-        <v>0.8688608946624842</v>
+        <v>0.9616302598932601</v>
       </c>
       <c r="D282" t="n">
-        <v>0.07647914244739951</v>
+        <v>0.02636835665458482</v>
       </c>
     </row>
     <row r="283">
@@ -4389,13 +4389,13 @@
         <v>2.81</v>
       </c>
       <c r="B283" t="n">
-        <v>1.646144010999607</v>
+        <v>1.723725601349726</v>
       </c>
       <c r="C283" t="n">
-        <v>0.8693541549522663</v>
+        <v>0.9641865223323575</v>
       </c>
       <c r="D283" t="n">
-        <v>0.07836470810570194</v>
+        <v>0.02731840721033738</v>
       </c>
     </row>
     <row r="284">
@@ -4403,13 +4403,13 @@
         <v>2.82</v>
       </c>
       <c r="B284" t="n">
-        <v>1.63346889944508</v>
+        <v>1.717610107578848</v>
       </c>
       <c r="C284" t="n">
-        <v>0.8697857533155827</v>
+        <v>0.9667541279035823</v>
       </c>
       <c r="D284" t="n">
-        <v>0.08027263686783592</v>
+        <v>0.02828426993868207</v>
       </c>
     </row>
     <row r="285">
@@ -4417,13 +4417,13 @@
         <v>2.83</v>
       </c>
       <c r="B285" t="n">
-        <v>1.620917473296632</v>
+        <v>1.711730104754383</v>
       </c>
       <c r="C285" t="n">
-        <v>0.8701545102737122</v>
+        <v>0.9693330393187577</v>
       </c>
       <c r="D285" t="n">
-        <v>0.08220303927362485</v>
+        <v>0.02926607534135951</v>
       </c>
     </row>
     <row r="286">
@@ -4431,13 +4431,13 @@
         <v>2.84</v>
       </c>
       <c r="B286" t="n">
-        <v>1.608490473064038</v>
+        <v>1.706087614270443</v>
       </c>
       <c r="C286" t="n">
-        <v>0.8704592579695282</v>
+        <v>0.9719232186157357</v>
       </c>
       <c r="D286" t="n">
-        <v>0.08415602586289189</v>
+        <v>0.03026395392011019</v>
       </c>
     </row>
     <row r="287">
@@ -4445,13 +4445,13 @@
         <v>2.85</v>
       </c>
       <c r="B287" t="n">
-        <v>1.596188591468174</v>
+        <v>1.700684697952388</v>
       </c>
       <c r="C287" t="n">
-        <v>0.8706988409895016</v>
+        <v>0.9745246271494928</v>
       </c>
       <c r="D287" t="n">
-        <v>0.08613170717546059</v>
+        <v>0.03127803617667477</v>
       </c>
     </row>
     <row r="288">
@@ -4459,13 +4459,13 @@
         <v>2.86</v>
       </c>
       <c r="B288" t="n">
-        <v>1.584012474827708</v>
+        <v>1.695523462580149</v>
       </c>
       <c r="C288" t="n">
-        <v>0.8708721171959496</v>
+        <v>0.9771372255832207</v>
       </c>
       <c r="D288" t="n">
-        <v>0.08813019375115407</v>
+        <v>0.03230845261279375</v>
       </c>
     </row>
     <row r="289">
@@ -4473,13 +4473,13 @@
         <v>2.87</v>
       </c>
       <c r="B289" t="n">
-        <v>1.571962724439515</v>
+        <v>1.690606064478489</v>
       </c>
       <c r="C289" t="n">
-        <v>0.8709779585689233</v>
+        <v>0.9797609738794163</v>
       </c>
       <c r="D289" t="n">
-        <v>0.09015159612979583</v>
+        <v>0.03335533373020778</v>
       </c>
     </row>
     <row r="290">
@@ -4487,13 +4487,13 @@
         <v>2.88</v>
       </c>
       <c r="B290" t="n">
-        <v>1.560039897952172</v>
+        <v>1.685934714179414</v>
       </c>
       <c r="C290" t="n">
-        <v>0.8710152520570965</v>
+        <v>0.982395831290969</v>
       </c>
       <c r="D290" t="n">
-        <v>0.09219602485120904</v>
+        <v>0.03441881003065735</v>
       </c>
     </row>
     <row r="291">
@@ -4501,13 +4501,13 @@
         <v>2.89</v>
       </c>
       <c r="B291" t="n">
-        <v>1.548244510731863</v>
+        <v>1.681511681162184</v>
       </c>
       <c r="C291" t="n">
-        <v>0.8709829004369953</v>
+        <v>0.9850417563522488</v>
       </c>
       <c r="D291" t="n">
-        <v>0.09426359045521722</v>
+        <v>0.03549901201588315</v>
       </c>
     </row>
     <row r="292">
@@ -4515,13 +4515,13 @@
         <v>2.9</v>
       </c>
       <c r="B292" t="n">
-        <v>1.536577037220115</v>
+        <v>1.677339298676711</v>
       </c>
       <c r="C292" t="n">
-        <v>0.8708798231798734</v>
+        <v>0.9876987068701926</v>
       </c>
       <c r="D292" t="n">
-        <v>0.09635440348164349</v>
+        <v>0.03659607018762562</v>
       </c>
     </row>
     <row r="293">
@@ -4529,13 +4529,13 @@
         <v>2.91</v>
       </c>
       <c r="B293" t="n">
-        <v>1.525037912282802</v>
+        <v>1.67341996865644</v>
       </c>
       <c r="C293" t="n">
-        <v>0.8707049573255231</v>
+        <v>0.9903666399153931</v>
       </c>
       <c r="D293" t="n">
-        <v>0.09846857447031142</v>
+        <v>0.03771011504762547</v>
       </c>
     </row>
     <row r="294">
@@ -4543,13 +4543,13 @@
         <v>2.92</v>
       </c>
       <c r="B294" t="n">
-        <v>1.513627532549888</v>
+        <v>1.669756166727132</v>
       </c>
       <c r="C294" t="n">
-        <v>0.8704572583622699</v>
+        <v>0.9930455118131887</v>
       </c>
       <c r="D294" t="n">
-        <v>0.1006062139610441</v>
+        <v>0.03884127709762315</v>
       </c>
     </row>
     <row r="295">
@@ -4557,13 +4557,13 @@
         <v>2.93</v>
       </c>
       <c r="B295" t="n">
-        <v>1.502346257745446</v>
+        <v>1.666350447318313</v>
       </c>
       <c r="C295" t="n">
-        <v>0.8701357011123879</v>
+        <v>0.9957352781347562</v>
       </c>
       <c r="D295" t="n">
-        <v>0.1027674324936651</v>
+        <v>0.03998968683935936</v>
       </c>
     </row>
     <row r="296">
@@ -4571,13 +4571,13 @@
         <v>2.94</v>
       </c>
       <c r="B296" t="n">
-        <v>1.491194412007496</v>
+        <v>1.663205448884519</v>
       </c>
       <c r="C296" t="n">
-        <v>0.8697392806221345</v>
+        <v>0.9984358936882058</v>
       </c>
       <c r="D296" t="n">
-        <v>0.1049523406079975</v>
+        <v>0.04115547477457456</v>
       </c>
     </row>
     <row r="297">
@@ -4585,13 +4585,13 @@
         <v>2.95</v>
       </c>
       <c r="B297" t="n">
-        <v>1.480172285197266</v>
+        <v>1.660323899243803</v>
       </c>
       <c r="C297" t="n">
-        <v>0.8692670130555838</v>
+        <v>1.001147312509683</v>
       </c>
       <c r="D297" t="n">
-        <v>0.1071610488438648</v>
+        <v>0.04233877140500945</v>
       </c>
     </row>
     <row r="298">
@@ -4599,13 +4599,13 @@
         <v>2.96</v>
       </c>
       <c r="B298" t="n">
-        <v>1.469280134197513</v>
+        <v>1.657708621041405</v>
       </c>
       <c r="C298" t="n">
-        <v>0.8687179365914135</v>
+        <v>1.003869487854474</v>
       </c>
       <c r="D298" t="n">
-        <v>0.1093936677410903</v>
+        <v>0.04353970723240448</v>
       </c>
     </row>
     <row r="299">
@@ -4613,13 +4613,13 @@
         <v>2.97</v>
       </c>
       <c r="B299" t="n">
-        <v>1.458518184199549</v>
+        <v>1.655362537346847</v>
       </c>
       <c r="C299" t="n">
-        <v>0.8680911123217666</v>
+        <v>1.006602372188116</v>
       </c>
       <c r="D299" t="n">
-        <v>0.1116503078394974</v>
+        <v>0.04475841275850033</v>
       </c>
     </row>
     <row r="300">
@@ -4627,13 +4627,13 @@
         <v>2.98</v>
       </c>
       <c r="B300" t="n">
-        <v>1.447886629978715</v>
+        <v>1.653288677393166</v>
       </c>
       <c r="C300" t="n">
-        <v>0.8673856251522984</v>
+        <v>1.009345917177517</v>
       </c>
       <c r="D300" t="n">
-        <v>0.1139310796789092</v>
+        <v>0.04599501848503749</v>
       </c>
     </row>
     <row r="301">
@@ -4641,13 +4641,13 @@
         <v>2.99</v>
       </c>
       <c r="B301" t="n">
-        <v>1.437385637157995</v>
+        <v>1.65149018246741</v>
       </c>
       <c r="C301" t="n">
-        <v>0.8666005847024819</v>
+        <v>1.012100073682085</v>
       </c>
       <c r="D301" t="n">
-        <v>0.1162360937991494</v>
+        <v>0.04724965491375662</v>
       </c>
     </row>
     <row r="302">
@@ -4655,13 +4655,13 @@
         <v>3</v>
       </c>
       <c r="B302" t="n">
-        <v>1.427015343459586</v>
+        <v>1.649970311962026</v>
       </c>
       <c r="C302" t="n">
-        <v>0.8657351262052321</v>
+        <v>1.014864791744859</v>
       </c>
       <c r="D302" t="n">
-        <v>0.1185654607400409</v>
+        <v>0.0485224525463982</v>
       </c>
     </row>
     <row r="303">
@@ -4669,13 +4669,13 @@
         <v>3.01</v>
       </c>
       <c r="B303" t="n">
-        <v>1.416775859944186</v>
+        <v>1.648732449597213</v>
       </c>
       <c r="C303" t="n">
-        <v>0.8647884114048794</v>
+        <v>1.017640020583661</v>
       </c>
       <c r="D303" t="n">
-        <v>0.1209192910414074</v>
+        <v>0.04981354188470293</v>
       </c>
     </row>
     <row r="304">
@@ -4683,13 +4683,13 @@
         <v>3.02</v>
       </c>
       <c r="B304" t="n">
-        <v>1.406667272237874</v>
+        <v>1.647780109824849</v>
       </c>
       <c r="C304" t="n">
-        <v>0.8637596294525077</v>
+        <v>1.020425708582249</v>
       </c>
       <c r="D304" t="n">
-        <v>0.123297695243072</v>
+        <v>0.05112305343041125</v>
       </c>
     </row>
     <row r="305">
@@ -4697,13 +4697,13 @@
         <v>3.03</v>
       </c>
       <c r="B305" t="n">
-        <v>1.396689641746425</v>
+        <v>1.647116944425134</v>
       </c>
       <c r="C305" t="n">
-        <v>0.8626479977976443</v>
+        <v>1.023221803281489</v>
       </c>
       <c r="D305" t="n">
-        <v>0.1257007838848582</v>
+        <v>0.05245111768526387</v>
       </c>
     </row>
     <row r="306">
@@ -4711,13 +4711,13 @@
         <v>3.04</v>
       </c>
       <c r="B306" t="n">
-        <v>1.386843006856967</v>
+        <v>1.646746749307641</v>
       </c>
       <c r="C306" t="n">
-        <v>0.8614527630752766</v>
+        <v>1.026028251370538</v>
       </c>
       <c r="D306" t="n">
-        <v>0.1281286675065892</v>
+        <v>0.05379786515100123</v>
       </c>
     </row>
     <row r="307">
@@ -4725,13 +4725,13 @@
         <v>3.05</v>
       </c>
       <c r="B307" t="n">
-        <v>1.377127384126917</v>
+        <v>1.646673471529081</v>
       </c>
       <c r="C307" t="n">
-        <v>0.8601732019871455</v>
+        <v>1.028844998678038</v>
       </c>
       <c r="D307" t="n">
-        <v>0.1305814566480885</v>
+        <v>0.05516342632936405</v>
       </c>
     </row>
     <row r="308">
@@ -4739,13 +4739,13 @@
         <v>3.06</v>
       </c>
       <c r="B308" t="n">
-        <v>1.367542769460132</v>
+        <v>1.646901216540693</v>
       </c>
       <c r="C308" t="n">
-        <v>0.8588086221762502</v>
+        <v>1.031671990163334</v>
       </c>
       <c r="D308" t="n">
-        <v>0.1330592618491791</v>
+        <v>0.05654793172209274</v>
       </c>
     </row>
     <row r="309">
@@ -4753,13 +4753,13 @@
         <v>3.07</v>
       </c>
       <c r="B309" t="n">
-        <v>1.358089139270288</v>
+        <v>1.647434255678847</v>
       </c>
       <c r="C309" t="n">
-        <v>0.8573583630934829</v>
+        <v>1.034509169907697</v>
       </c>
       <c r="D309" t="n">
-        <v>0.1355621936496847</v>
+        <v>0.05795151183092807</v>
       </c>
     </row>
     <row r="310">
@@ -4767,13 +4767,13 @@
         <v>3.08</v>
       </c>
       <c r="B310" t="n">
-        <v>1.348766451631489</v>
+        <v>1.648277033913134</v>
       </c>
       <c r="C310" t="n">
-        <v>0.8558217968552926</v>
+        <v>1.037356481105575</v>
       </c>
       <c r="D310" t="n">
-        <v>0.1380903625894284</v>
+        <v>0.05937429715761043</v>
       </c>
     </row>
     <row r="311">
@@ -4781,13 +4781,13 @@
         <v>3.09</v>
       </c>
       <c r="B311" t="n">
-        <v>1.339574647416138</v>
+        <v>1.649434177866932</v>
       </c>
       <c r="C311" t="n">
-        <v>0.8541983290912678</v>
+        <v>1.04021386605586</v>
       </c>
       <c r="D311" t="n">
-        <v>0.1406438792082336</v>
+        <v>0.06081641820388051</v>
       </c>
     </row>
     <row r="312">
@@ -4795,13 +4795,13 @@
         <v>3.1</v>
       </c>
       <c r="B312" t="n">
-        <v>1.330513651420156</v>
+        <v>1.650910504126263</v>
       </c>
       <c r="C312" t="n">
-        <v>0.8524873997805096</v>
+        <v>1.04308126615317</v>
       </c>
       <c r="D312" t="n">
-        <v>0.1432228540459237</v>
+        <v>0.06227800547147888</v>
       </c>
     </row>
     <row r="313">
@@ -4809,13 +4809,13 @@
         <v>3.11</v>
       </c>
       <c r="B313" t="n">
-        <v>1.321583373475643</v>
+        <v>1.652711027853514</v>
       </c>
       <c r="C313" t="n">
-        <v>0.8506884840756588</v>
+        <v>1.045958621879159</v>
       </c>
       <c r="D313" t="n">
-        <v>0.1458273976423219</v>
+        <v>0.06375918946214607</v>
       </c>
     </row>
     <row r="314">
@@ -4823,13 +4823,13 @@
         <v>3.12</v>
       </c>
       <c r="B314" t="n">
-        <v>1.312783709551083</v>
+        <v>1.65484097172349</v>
       </c>
       <c r="C314" t="n">
-        <v>0.8488010931134252</v>
+        <v>1.048845872793847</v>
       </c>
       <c r="D314" t="n">
-        <v>0.1484576205372518</v>
+        <v>0.06526010067762271</v>
       </c>
     </row>
     <row r="315">
@@ -4837,13 +4837,13 @@
         <v>3.13</v>
       </c>
       <c r="B315" t="n">
-        <v>1.304114542839255</v>
+        <v>1.657305775200187</v>
       </c>
       <c r="C315" t="n">
-        <v>0.8468247748104657</v>
+        <v>1.051742957526972</v>
       </c>
       <c r="D315" t="n">
-        <v>0.1511136332705363</v>
+        <v>0.06678086961964931</v>
       </c>
     </row>
     <row r="316">
@@ -4851,13 +4851,13 @@
         <v>3.14</v>
       </c>
       <c r="B316" t="n">
-        <v>1.295575744833021</v>
+        <v>1.660111104173619</v>
       </c>
       <c r="C316" t="n">
-        <v>0.8447591146434399</v>
+        <v>1.054649813769373</v>
       </c>
       <c r="D316" t="n">
-        <v>0.1537955463819991</v>
+        <v>0.06832162678996653</v>
       </c>
     </row>
     <row r="317">
@@ -4865,13 +4865,13 @@
         <v>3.15</v>
       </c>
       <c r="B317" t="n">
-        <v>1.287167176389165</v>
+        <v>1.663262860977065</v>
       </c>
       <c r="C317" t="n">
-        <v>0.8426037364120773</v>
+        <v>1.05756637826439</v>
       </c>
       <c r="D317" t="n">
-        <v>0.1565034704114633</v>
+        <v>0.06988250269031483</v>
       </c>
     </row>
     <row r="318">
@@ -4879,13 +4879,13 @@
         <v>3.16</v>
       </c>
       <c r="B318" t="n">
-        <v>1.278888688780522</v>
+        <v>1.666767194806199</v>
       </c>
       <c r="C318" t="n">
-        <v>0.8403583029840749</v>
+        <v>1.060492586799302</v>
       </c>
       <c r="D318" t="n">
-        <v>0.1592375158987525</v>
+        <v>0.07146362782243496</v>
       </c>
     </row>
     <row r="319">
@@ -4893,13 +4893,13 @@
         <v>3.17</v>
       </c>
       <c r="B319" t="n">
-        <v>1.270740124736624</v>
+        <v>1.67063051256267</v>
       </c>
       <c r="C319" t="n">
-        <v>0.8380225170206484</v>
+        <v>1.063428374196787</v>
       </c>
       <c r="D319" t="n">
-        <v>0.1619977933836898</v>
+        <v>0.07306513268806729</v>
       </c>
     </row>
     <row r="320">
@@ -4907,13 +4907,13 @@
         <v>3.18</v>
       </c>
       <c r="B320" t="n">
-        <v>1.262721319473119</v>
+        <v>1.674859490145979</v>
       </c>
       <c r="C320" t="n">
-        <v>0.8355961216815576</v>
+        <v>1.066373674306414</v>
       </c>
       <c r="D320" t="n">
-        <v>0.1647844134060986</v>
+        <v>0.07468714778895258</v>
       </c>
     </row>
     <row r="321">
@@ -4921,13 +4921,13 @@
         <v>3.19</v>
       </c>
       <c r="B321" t="n">
-        <v>1.254832101710272</v>
+        <v>1.679461084218722</v>
       </c>
       <c r="C321" t="n">
-        <v>0.8330789013084244</v>
+        <v>1.069328419996169</v>
       </c>
       <c r="D321" t="n">
-        <v>0.1675974865058021</v>
+        <v>0.07632980362683123</v>
       </c>
     </row>
     <row r="322">
@@ -4935,13 +4935,13 @@
         <v>3.2</v>
       </c>
       <c r="B322" t="n">
-        <v>1.247072294680811</v>
+        <v>1.684442544471669</v>
       </c>
       <c r="C322" t="n">
-        <v>0.8304706820851676</v>
+        <v>1.072292543144015</v>
       </c>
       <c r="D322" t="n">
-        <v>0.170437123222624</v>
+        <v>0.07799323070344404</v>
       </c>
     </row>
     <row r="323">
@@ -4949,13 +4949,13 @@
         <v>3.21</v>
       </c>
       <c r="B323" t="n">
-        <v>1.239441717127493</v>
+        <v>1.689811426416593</v>
       </c>
       <c r="C323" t="n">
-        <v>0.8277713326743811</v>
+        <v>1.075265974629478</v>
       </c>
       <c r="D323" t="n">
-        <v>0.1733034340963872</v>
+        <v>0.07967755952053132</v>
       </c>
     </row>
     <row r="324">
@@ -4963,13 +4963,13 @@
         <v>3.22</v>
       </c>
       <c r="B324" t="n">
-        <v>1.231940184290688</v>
+        <v>1.695575604736289</v>
       </c>
       <c r="C324" t="n">
-        <v>0.8249807648284906</v>
+        <v>1.078248644325283</v>
       </c>
       <c r="D324" t="n">
-        <v>0.1761965296669154</v>
+        <v>0.08138292057983391</v>
       </c>
     </row>
     <row r="325">
@@ -4977,13 +4977,13 @@
         <v>3.23</v>
       </c>
       <c r="B325" t="n">
-        <v>1.224567508886395</v>
+        <v>1.701743287222848</v>
       </c>
       <c r="C325" t="n">
-        <v>0.8220989339745275</v>
+        <v>1.081240481089018</v>
       </c>
       <c r="D325" t="n">
-        <v>0.1791165204740316</v>
+        <v>0.08310944438309217</v>
       </c>
     </row>
     <row r="326">
@@ -4991,13 +4991,13 @@
         <v>3.24</v>
       </c>
       <c r="B326" t="n">
-        <v>1.217323502075034</v>
+        <v>1.708323029337001</v>
       </c>
       <c r="C326" t="n">
-        <v>0.8191258397713752</v>
+        <v>1.084241412754836</v>
       </c>
       <c r="D326" t="n">
-        <v>0.1820635170575594</v>
+        <v>0.08485726143204682</v>
       </c>
     </row>
     <row r="327">
@@ -5005,13 +5005,13 @@
         <v>3.25</v>
       </c>
       <c r="B327" t="n">
-        <v>1.210207974421457</v>
+        <v>1.715323749423148</v>
       </c>
       <c r="C327" t="n">
-        <v>0.8160615266383482</v>
+        <v>1.087251366125206</v>
       </c>
       <c r="D327" t="n">
-        <v>0.1850376299573219</v>
+        <v>0.08662650222843835</v>
       </c>
     </row>
     <row r="328">
@@ -5019,13 +5019,13 @@
         <v>3.26</v>
       </c>
       <c r="B328" t="n">
-        <v>1.203220736846576</v>
+        <v>1.722754744616674</v>
       </c>
       <c r="C328" t="n">
-        <v>0.8129060842539859</v>
+        <v>1.090270266962698</v>
       </c>
       <c r="D328" t="n">
-        <v>0.1880389697131427</v>
+        <v>0.08841729727400741</v>
       </c>
     </row>
     <row r="329">
@@ -5033,13 +5033,13 @@
         <v>3.27</v>
       </c>
       <c r="B329" t="n">
-        <v>1.196361601571083</v>
+        <v>1.730625707482194</v>
       </c>
       <c r="C329" t="n">
-        <v>0.8096596480239533</v>
+        <v>1.093298039981818</v>
       </c>
       <c r="D329" t="n">
-        <v>0.1910676468648449</v>
+        <v>0.09022977707049448</v>
       </c>
     </row>
     <row r="330">
@@ -5047,13 +5047,13 @@
         <v>3.28</v>
       </c>
       <c r="B330" t="n">
-        <v>1.189630383051694</v>
+        <v>1.738946743423587</v>
       </c>
       <c r="C330" t="n">
-        <v>0.8063223995169599</v>
+        <v>1.096334608840881</v>
       </c>
       <c r="D330" t="n">
-        <v>0.194123771952252</v>
+        <v>0.09206407211964024</v>
       </c>
     </row>
     <row r="331">
@@ -5061,13 +5061,13 @@
         <v>3.29</v>
       </c>
       <c r="B331" t="n">
-        <v>1.183026898910441</v>
+        <v>1.74772838890899</v>
       </c>
       <c r="C331" t="n">
-        <v>0.8028945668676352</v>
+        <v>1.099379896133938</v>
       </c>
       <c r="D331" t="n">
-        <v>0.1972074555151871</v>
+        <v>0.09392031292318516</v>
       </c>
     </row>
     <row r="332">
@@ -5075,13 +5075,13 @@
         <v>3.3</v>
       </c>
       <c r="B332" t="n">
-        <v>1.17655097085747</v>
+        <v>1.756981630556463</v>
       </c>
       <c r="C332" t="n">
-        <v>0.7993764251453113</v>
+        <v>1.102433823382751</v>
       </c>
       <c r="D332" t="n">
-        <v>0.2003188080934739</v>
+        <v>0.09579862998286996</v>
       </c>
     </row>
     <row r="333">
@@ -5089,13 +5089,13 @@
         <v>3.31</v>
       </c>
       <c r="B333" t="n">
-        <v>1.170202425607918</v>
+        <v>1.766717925128589</v>
       </c>
       <c r="C333" t="n">
-        <v>0.7957682966876971</v>
+        <v>1.10549631102881</v>
       </c>
       <c r="D333" t="n">
-        <v>0.2034579402269353</v>
+        <v>0.09769915380043503</v>
       </c>
     </row>
     <row r="334">
@@ -5103,13 +5103,13 @@
         <v>3.32</v>
       </c>
       <c r="B334" t="n">
-        <v>1.163981095793367</v>
+        <v>1.77694922048719</v>
       </c>
       <c r="C334" t="n">
-        <v>0.7920705513984488</v>
+        <v>1.108567278425412</v>
       </c>
       <c r="D334" t="n">
-        <v>0.2066249624553951</v>
+        <v>0.09962201487762117</v>
       </c>
     </row>
     <row r="335">
@@ -5117,13 +5117,13 @@
         <v>3.33</v>
       </c>
       <c r="B335" t="n">
-        <v>1.157886820868463</v>
+        <v>1.787687977562227</v>
       </c>
       <c r="C335" t="n">
-        <v>0.7882836070076787</v>
+        <v>1.111646643829786</v>
       </c>
       <c r="D335" t="n">
-        <v>0.2098199853186761</v>
+        <v>0.1015673437161687</v>
       </c>
     </row>
     <row r="336">
@@ -5131,13 +5131,13 @@
         <v>3.34</v>
       </c>
       <c r="B336" t="n">
-        <v>1.151919448013266</v>
+        <v>1.798947193392222</v>
       </c>
       <c r="C336" t="n">
-        <v>0.7844079292944605</v>
+        <v>1.114734324395281</v>
       </c>
       <c r="D336" t="n">
-        <v>0.213043119356602</v>
+        <v>0.1035352708178184</v>
       </c>
     </row>
     <row r="337">
@@ -5145,13 +5145,13 @@
         <v>3.35</v>
       </c>
       <c r="B337" t="n">
-        <v>1.146078833031943</v>
+        <v>1.81074042529685</v>
       </c>
       <c r="C337" t="n">
-        <v>0.7804440322704458</v>
+        <v>1.117830236163599</v>
       </c>
       <c r="D337" t="n">
-        <v>0.2162944751089961</v>
+        <v>0.1055259266843108</v>
       </c>
     </row>
     <row r="338">
@@ -5159,13 +5159,13 @@
         <v>3.36</v>
       </c>
       <c r="B338" t="n">
-        <v>1.140364841248404</v>
+        <v>1.823081816246009</v>
       </c>
       <c r="C338" t="n">
-        <v>0.776392478323718</v>
+        <v>1.120934294057101</v>
       </c>
       <c r="D338" t="n">
-        <v>0.2195741631156816</v>
+        <v>0.1075394418173864</v>
       </c>
     </row>
     <row r="339">
@@ -5173,13 +5173,13 @@
         <v>3.37</v>
       </c>
       <c r="B339" t="n">
-        <v>1.134777348399545</v>
+        <v>1.835986121493499</v>
       </c>
       <c r="C339" t="n">
-        <v>0.7722538783220616</v>
+        <v>1.124046411871162</v>
       </c>
       <c r="D339" t="n">
-        <v>0.2228822939164821</v>
+        <v>0.1095759467187859</v>
       </c>
     </row>
     <row r="340">
@@ -5187,13 +5187,13 @@
         <v>3.38</v>
       </c>
       <c r="B340" t="n">
-        <v>1.129316241526721</v>
+        <v>1.849468736547518</v>
       </c>
       <c r="C340" t="n">
-        <v>0.7680288916748669</v>
+        <v>1.127166502266593</v>
       </c>
       <c r="D340" t="n">
-        <v>0.2262189780512205</v>
+        <v>0.1116355718902497</v>
       </c>
     </row>
     <row r="341">
@@ -5201,13 +5201,13 @@
         <v>3.39</v>
       </c>
       <c r="B341" t="n">
-        <v>1.123981419866161</v>
+        <v>1.863545726554556</v>
       </c>
       <c r="C341" t="n">
-        <v>0.7637182263529156</v>
+        <v>1.130294476762127</v>
       </c>
       <c r="D341" t="n">
-        <v>0.2295843260597206</v>
+        <v>0.1137184478335186</v>
       </c>
     </row>
     <row r="342">
@@ -5215,13 +5215,13 @@
         <v>3.4</v>
       </c>
       <c r="B342" t="n">
-        <v>1.118772795739002</v>
+        <v>1.878233857177907</v>
       </c>
       <c r="C342" t="n">
-        <v>0.7593226388653596</v>
+        <v>1.133430245726969</v>
       </c>
       <c r="D342" t="n">
-        <v>0.2329784484818053</v>
+        <v>0.115824705050333</v>
       </c>
     </row>
     <row r="343">
@@ -5229,13 +5229,13 @@
         <v>3.41</v>
       </c>
       <c r="B343" t="n">
-        <v>1.113690295441671</v>
+        <v>1.893550627056985</v>
       </c>
       <c r="C343" t="n">
-        <v>0.7548429341932306</v>
+        <v>1.136573718373416</v>
       </c>
       <c r="D343" t="n">
-        <v>0.2364014558572983</v>
+        <v>0.1179544740424336</v>
       </c>
     </row>
     <row r="344">
@@ -5243,13 +5243,13 @@
         <v>3.42</v>
       </c>
       <c r="B344" t="n">
-        <v>1.10873386013734</v>
+        <v>1.909514301938867</v>
       </c>
       <c r="C344" t="n">
-        <v>0.7502799656788812</v>
+        <v>1.139724802749544</v>
       </c>
       <c r="D344" t="n">
-        <v>0.2398534587260226</v>
+        <v>0.1201078853115608</v>
       </c>
     </row>
     <row r="345">
@@ -5257,13 +5257,13 @@
         <v>3.43</v>
       </c>
       <c r="B345" t="n">
-        <v>1.103903446749236</v>
+        <v>1.926143950579187</v>
       </c>
       <c r="C345" t="n">
-        <v>0.7456346348707961</v>
+        <v>1.142883405731971</v>
       </c>
       <c r="D345" t="n">
-        <v>0.2433345676278019</v>
+        <v>0.1222850693594554</v>
       </c>
     </row>
     <row r="346">
@@ -5271,13 +5271,13 @@
         <v>3.44</v>
       </c>
       <c r="B346" t="n">
-        <v>1.099199028856574</v>
+        <v>1.943459482515432</v>
       </c>
       <c r="C346" t="n">
-        <v>0.7409078913232766</v>
+        <v>1.146049433018682</v>
       </c>
       <c r="D346" t="n">
-        <v>0.2468448931024591</v>
+        <v>0.1244861566878577</v>
       </c>
     </row>
     <row r="347">
@@ -5285,13 +5285,13 @@
         <v>3.45</v>
       </c>
       <c r="B347" t="n">
-        <v>1.094620597593922</v>
+        <v>1.961481687822187</v>
       </c>
       <c r="C347" t="n">
-        <v>0.7361007323505424</v>
+        <v>1.149222789121947</v>
       </c>
       <c r="D347" t="n">
-        <v>0.250384545689818</v>
+        <v>0.1267112777985086</v>
       </c>
     </row>
     <row r="348">
@@ -5299,13 +5299,13 @@
         <v>3.46</v>
       </c>
       <c r="B348" t="n">
-        <v>1.090168162554832</v>
+        <v>1.980232278964634</v>
       </c>
       <c r="C348" t="n">
-        <v>0.7312142027348584</v>
+        <v>1.152403377361299</v>
       </c>
       <c r="D348" t="n">
-        <v>0.2539536359297015</v>
+        <v>0.1289605631931485</v>
       </c>
     </row>
     <row r="349">
@@ -5313,13 +5313,13 @@
         <v>3.47</v>
       </c>
       <c r="B349" t="n">
-        <v>1.085841752700582</v>
+        <v>1.999733934873996</v>
       </c>
       <c r="C349" t="n">
-        <v>0.7262493943883517</v>
+        <v>1.155591099856601</v>
       </c>
       <c r="D349" t="n">
-        <v>0.2575522743619333</v>
+        <v>0.131234143373518</v>
       </c>
     </row>
     <row r="350">
@@ -5327,13 +5327,13 @@
         <v>3.48</v>
       </c>
       <c r="B350" t="n">
-        <v>1.081641417274914</v>
+        <v>2.020010347376372</v>
       </c>
       <c r="C350" t="n">
-        <v>0.7212074459682357</v>
+        <v>1.158785857521192</v>
       </c>
       <c r="D350" t="n">
-        <v>0.2611805715263364</v>
+        <v>0.1335321488413576</v>
       </c>
     </row>
     <row r="351">
@@ -5341,13 +5341,13 @@
         <v>3.49</v>
       </c>
       <c r="B351" t="n">
-        <v>1.077567226725665</v>
+        <v>2.041086270114746</v>
       </c>
       <c r="C351" t="n">
-        <v>0.7160895424452274</v>
+        <v>1.161987550055111</v>
       </c>
       <c r="D351" t="n">
-        <v>0.2648386379627345</v>
+        <v>0.1358547100984079</v>
       </c>
     </row>
     <row r="352">
@@ -5355,13 +5355,13 @@
         <v>3.5</v>
       </c>
       <c r="B352" t="n">
-        <v>1.073619273634224</v>
+        <v>2.062987570112898</v>
       </c>
       <c r="C352" t="n">
-        <v>0.7108969146249989</v>
+        <v>1.165196075938416</v>
       </c>
       <c r="D352" t="n">
-        <v>0.2685265842109505</v>
+        <v>0.1382019576464096</v>
       </c>
     </row>
   </sheetData>
